--- a/research/traditional_assets/database/data/netherlands/netherlands_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07129124021041604</v>
+        <v>0.07114069881067318</v>
       </c>
       <c r="C2">
-        <v>384.364782449445</v>
+        <v>381.8250838599292</v>
       </c>
       <c r="D2">
-        <v>345.464782449445</v>
+        <v>347.5170838599292</v>
       </c>
       <c r="E2">
-        <v>-149.5</v>
+        <v>-144.908</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.592</v>
       </c>
       <c r="G2">
         <v>38.9</v>
@@ -1451,28 +1451,28 @@
         <v>51.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2309776</v>
       </c>
       <c r="N2">
-        <v>51.4</v>
+        <v>51.1690224</v>
       </c>
       <c r="O2">
-        <v>13.2612</v>
+        <v>13.2016077792</v>
       </c>
       <c r="P2">
-        <v>38.1388</v>
+        <v>37.9674146208</v>
       </c>
       <c r="Q2">
-        <v>88.2388</v>
+        <v>88.06741462080001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07129124021041604</v>
+        <v>0.07148229576835674</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442502</v>
+        <v>0.5931246135879152</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>222.5324014103532</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07114069881067318</v>
+        <v>0.07099015741093029</v>
       </c>
       <c r="C3">
-        <v>381.8250838599292</v>
+        <v>379.3099151947005</v>
       </c>
       <c r="D3">
-        <v>347.5170838599292</v>
+        <v>349.5939151947005</v>
       </c>
       <c r="E3">
-        <v>-144.908</v>
+        <v>-140.316</v>
       </c>
       <c r="F3">
-        <v>4.592</v>
+        <v>9.183999999999999</v>
       </c>
       <c r="G3">
         <v>38.9</v>
@@ -1533,28 +1533,28 @@
         <v>51.4</v>
       </c>
       <c r="M3">
-        <v>0.2309776</v>
+        <v>0.4619552</v>
       </c>
       <c r="N3">
-        <v>51.1690224</v>
+        <v>50.9380448</v>
       </c>
       <c r="O3">
-        <v>13.2016077792</v>
+        <v>13.1420155584</v>
       </c>
       <c r="P3">
-        <v>37.9674146208</v>
+        <v>37.7960292416</v>
       </c>
       <c r="Q3">
-        <v>88.06741462080001</v>
+        <v>87.89602924159999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07148229576835674</v>
+        <v>0.07167725041931662</v>
       </c>
       <c r="T3">
-        <v>0.5931246135879152</v>
+        <v>0.5976270304692061</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>222.5324014103532</v>
+        <v>111.2662007051766</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07099015741093029</v>
+        <v>0.07083961601118741</v>
       </c>
       <c r="C4">
-        <v>379.3099151947005</v>
+        <v>376.8197188849604</v>
       </c>
       <c r="D4">
-        <v>349.5939151947005</v>
+        <v>351.6957188849605</v>
       </c>
       <c r="E4">
-        <v>-140.316</v>
+        <v>-135.724</v>
       </c>
       <c r="F4">
-        <v>9.183999999999999</v>
+        <v>13.776</v>
       </c>
       <c r="G4">
         <v>38.9</v>
@@ -1615,28 +1615,28 @@
         <v>51.4</v>
       </c>
       <c r="M4">
-        <v>0.4619552</v>
+        <v>0.6929327999999999</v>
       </c>
       <c r="N4">
-        <v>50.9380448</v>
+        <v>50.7070672</v>
       </c>
       <c r="O4">
-        <v>13.1420155584</v>
+        <v>13.0824233376</v>
       </c>
       <c r="P4">
-        <v>37.7960292416</v>
+        <v>37.6246438624</v>
       </c>
       <c r="Q4">
-        <v>87.89602924159999</v>
+        <v>87.7246438624</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07167725041931662</v>
+        <v>0.07187622475380145</v>
       </c>
       <c r="T4">
-        <v>0.5976270304692061</v>
+        <v>0.6022222806882553</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>111.2662007051766</v>
+        <v>74.17746713678441</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07083961601118741</v>
+        <v>0.07068907461144455</v>
       </c>
       <c r="C5">
-        <v>376.8197188849604</v>
+        <v>374.3549480660794</v>
       </c>
       <c r="D5">
-        <v>351.6957188849605</v>
+        <v>353.8229480660794</v>
       </c>
       <c r="E5">
-        <v>-135.724</v>
+        <v>-131.132</v>
       </c>
       <c r="F5">
-        <v>13.776</v>
+        <v>18.368</v>
       </c>
       <c r="G5">
         <v>38.9</v>
@@ -1697,28 +1697,28 @@
         <v>51.4</v>
       </c>
       <c r="M5">
-        <v>0.6929327999999999</v>
+        <v>0.9239103999999999</v>
       </c>
       <c r="N5">
-        <v>50.7070672</v>
+        <v>50.4760896</v>
       </c>
       <c r="O5">
-        <v>13.0824233376</v>
+        <v>13.0228311168</v>
       </c>
       <c r="P5">
-        <v>37.6246438624</v>
+        <v>37.4532584832</v>
       </c>
       <c r="Q5">
-        <v>87.7246438624</v>
+        <v>87.55325848320001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07187622475380145</v>
+        <v>0.0720793443869214</v>
       </c>
       <c r="T5">
-        <v>0.6022222806882553</v>
+        <v>0.6069132652868683</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.17746713678441</v>
+        <v>55.63310035258831</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07068907461144455</v>
+        <v>0.07053853321170167</v>
       </c>
       <c r="C6">
-        <v>374.3549480660794</v>
+        <v>371.9160669032878</v>
       </c>
       <c r="D6">
-        <v>353.8229480660794</v>
+        <v>355.9760669032878</v>
       </c>
       <c r="E6">
-        <v>-131.132</v>
+        <v>-126.54</v>
       </c>
       <c r="F6">
-        <v>18.368</v>
+        <v>22.96</v>
       </c>
       <c r="G6">
         <v>38.9</v>
@@ -1779,28 +1779,28 @@
         <v>51.4</v>
       </c>
       <c r="M6">
-        <v>0.9239103999999999</v>
+        <v>1.154888</v>
       </c>
       <c r="N6">
-        <v>50.4760896</v>
+        <v>50.245112</v>
       </c>
       <c r="O6">
-        <v>13.0228311168</v>
+        <v>12.963238896</v>
       </c>
       <c r="P6">
-        <v>37.4532584832</v>
+        <v>37.281873104</v>
       </c>
       <c r="Q6">
-        <v>87.55325848320001</v>
+        <v>87.38187310399999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0720793443869214</v>
+        <v>0.07228674022284387</v>
       </c>
       <c r="T6">
-        <v>0.6069132652868683</v>
+        <v>0.6117030074559784</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.63310035258831</v>
+        <v>44.50648028207065</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07053853321170167</v>
+        <v>0.07038799181195879</v>
       </c>
       <c r="C7">
-        <v>371.9160669032878</v>
+        <v>369.5035509293286</v>
       </c>
       <c r="D7">
-        <v>355.9760669032878</v>
+        <v>358.1555509293286</v>
       </c>
       <c r="E7">
-        <v>-126.54</v>
+        <v>-121.948</v>
       </c>
       <c r="F7">
-        <v>22.96</v>
+        <v>27.552</v>
       </c>
       <c r="G7">
         <v>38.9</v>
@@ -1861,28 +1861,28 @@
         <v>51.4</v>
       </c>
       <c r="M7">
-        <v>1.154888</v>
+        <v>1.3858656</v>
       </c>
       <c r="N7">
-        <v>50.245112</v>
+        <v>50.0141344</v>
       </c>
       <c r="O7">
-        <v>12.963238896</v>
+        <v>12.9036466752</v>
       </c>
       <c r="P7">
-        <v>37.281873104</v>
+        <v>37.1104877248</v>
       </c>
       <c r="Q7">
-        <v>87.38187310399999</v>
+        <v>87.2104877248</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07228674022284387</v>
+        <v>0.07249854873612638</v>
       </c>
       <c r="T7">
-        <v>0.6117030074559784</v>
+        <v>0.6165946590329417</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.50648028207065</v>
+        <v>37.0887335683922</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07038799181195879</v>
+        <v>0.07023745041221592</v>
       </c>
       <c r="C8">
-        <v>369.5035509293286</v>
+        <v>367.1178873945937</v>
       </c>
       <c r="D8">
-        <v>358.1555509293286</v>
+        <v>360.3618873945937</v>
       </c>
       <c r="E8">
-        <v>-121.948</v>
+        <v>-117.356</v>
       </c>
       <c r="F8">
-        <v>27.552</v>
+        <v>32.144</v>
       </c>
       <c r="G8">
         <v>38.9</v>
@@ -1943,28 +1943,28 @@
         <v>51.4</v>
       </c>
       <c r="M8">
-        <v>1.3858656</v>
+        <v>1.6168432</v>
       </c>
       <c r="N8">
-        <v>50.0141344</v>
+        <v>49.7831568</v>
       </c>
       <c r="O8">
-        <v>12.9036466752</v>
+        <v>12.8440544544</v>
       </c>
       <c r="P8">
-        <v>37.1104877248</v>
+        <v>36.9391023456</v>
       </c>
       <c r="Q8">
-        <v>87.2104877248</v>
+        <v>87.0391023456</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07249854873612638</v>
+        <v>0.07271491227119992</v>
       </c>
       <c r="T8">
-        <v>0.6165946590329417</v>
+        <v>0.6215915074180119</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.08873356839221</v>
+        <v>31.79034305862189</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07023745041221592</v>
+        <v>0.07008690901247307</v>
       </c>
       <c r="C9">
-        <v>367.1178873945937</v>
+        <v>364.7595756302806</v>
       </c>
       <c r="D9">
-        <v>360.3618873945937</v>
+        <v>362.5955756302806</v>
       </c>
       <c r="E9">
-        <v>-117.356</v>
+        <v>-112.764</v>
       </c>
       <c r="F9">
-        <v>32.14400000000001</v>
+        <v>36.736</v>
       </c>
       <c r="G9">
         <v>38.9</v>
@@ -2025,28 +2025,28 @@
         <v>51.4</v>
       </c>
       <c r="M9">
-        <v>1.6168432</v>
+        <v>1.8478208</v>
       </c>
       <c r="N9">
-        <v>49.7831568</v>
+        <v>49.5521792</v>
       </c>
       <c r="O9">
-        <v>12.8440544544</v>
+        <v>12.7844622336</v>
       </c>
       <c r="P9">
-        <v>36.9391023456</v>
+        <v>36.7677169664</v>
       </c>
       <c r="Q9">
-        <v>87.0391023456</v>
+        <v>86.8677169664</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07271491227119992</v>
+        <v>0.07293597936138375</v>
       </c>
       <c r="T9">
-        <v>0.6215915074180119</v>
+        <v>0.6266969829418879</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.79034305862189</v>
+        <v>27.81655017629415</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07008690901247307</v>
+        <v>0.06993636761273017</v>
       </c>
       <c r="C10">
-        <v>364.7595756302806</v>
+        <v>362.4291274251403</v>
       </c>
       <c r="D10">
-        <v>362.5955756302806</v>
+        <v>364.8571274251403</v>
       </c>
       <c r="E10">
-        <v>-112.764</v>
+        <v>-108.172</v>
       </c>
       <c r="F10">
-        <v>36.736</v>
+        <v>41.328</v>
       </c>
       <c r="G10">
         <v>38.9</v>
@@ -2107,28 +2107,28 @@
         <v>51.4</v>
       </c>
       <c r="M10">
-        <v>1.8478208</v>
+        <v>2.0787984</v>
       </c>
       <c r="N10">
-        <v>49.5521792</v>
+        <v>49.3212016</v>
       </c>
       <c r="O10">
-        <v>12.7844622336</v>
+        <v>12.7248700128</v>
       </c>
       <c r="P10">
-        <v>36.7677169664</v>
+        <v>36.5963315872</v>
       </c>
       <c r="Q10">
-        <v>86.8677169664</v>
+        <v>86.69633158720001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07293597936138375</v>
+        <v>0.07316190506893426</v>
       </c>
       <c r="T10">
-        <v>0.6266969829418879</v>
+        <v>0.631914666719036</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.81655017629415</v>
+        <v>24.72582237892814</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06993636761273017</v>
+        <v>0.0697858262129873</v>
       </c>
       <c r="C11">
-        <v>362.4291274251403</v>
+        <v>360.127067416409</v>
       </c>
       <c r="D11">
-        <v>364.8571274251403</v>
+        <v>367.1470674164091</v>
       </c>
       <c r="E11">
-        <v>-108.172</v>
+        <v>-103.58</v>
       </c>
       <c r="F11">
-        <v>41.328</v>
+        <v>45.91999999999999</v>
       </c>
       <c r="G11">
         <v>38.9</v>
@@ -2189,28 +2189,28 @@
         <v>51.4</v>
       </c>
       <c r="M11">
-        <v>2.0787984</v>
+        <v>2.309776</v>
       </c>
       <c r="N11">
-        <v>49.3212016</v>
+        <v>49.090224</v>
       </c>
       <c r="O11">
-        <v>12.7248700128</v>
+        <v>12.665277792</v>
       </c>
       <c r="P11">
-        <v>36.5963315872</v>
+        <v>36.424946208</v>
       </c>
       <c r="Q11">
-        <v>86.69633158720001</v>
+        <v>86.524946208</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07316190506893426</v>
+        <v>0.07339285134776367</v>
       </c>
       <c r="T11">
-        <v>0.631914666719036</v>
+        <v>0.6372482990245651</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.72582237892814</v>
+        <v>22.25324014103532</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0697858262129873</v>
+        <v>0.06963528481324444</v>
       </c>
       <c r="C12">
-        <v>360.127067416409</v>
+        <v>357.8539334955609</v>
       </c>
       <c r="D12">
-        <v>367.1470674164091</v>
+        <v>369.4659334955609</v>
       </c>
       <c r="E12">
-        <v>-103.58</v>
+        <v>-98.988</v>
       </c>
       <c r="F12">
-        <v>45.92</v>
+        <v>50.512</v>
       </c>
       <c r="G12">
         <v>38.9</v>
@@ -2271,28 +2271,28 @@
         <v>51.4</v>
       </c>
       <c r="M12">
-        <v>2.309776</v>
+        <v>2.5407536</v>
       </c>
       <c r="N12">
-        <v>49.090224</v>
+        <v>48.8592464</v>
       </c>
       <c r="O12">
-        <v>12.665277792</v>
+        <v>12.6056855712</v>
       </c>
       <c r="P12">
-        <v>36.424946208</v>
+        <v>36.2535608288</v>
       </c>
       <c r="Q12">
-        <v>86.524946208</v>
+        <v>86.3535608288</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07339285134776367</v>
+        <v>0.07362898743061172</v>
       </c>
       <c r="T12">
-        <v>0.6372482990245651</v>
+        <v>0.6427017882358363</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.25324014103532</v>
+        <v>20.23021831003211</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06963528481324444</v>
+        <v>0.06948474341350155</v>
       </c>
       <c r="C13">
-        <v>357.8539334955609</v>
+        <v>355.6102772295287</v>
       </c>
       <c r="D13">
-        <v>369.4659334955609</v>
+        <v>371.8142772295287</v>
       </c>
       <c r="E13">
-        <v>-98.988</v>
+        <v>-94.396</v>
       </c>
       <c r="F13">
-        <v>50.512</v>
+        <v>55.104</v>
       </c>
       <c r="G13">
         <v>38.9</v>
@@ -2353,28 +2353,28 @@
         <v>51.4</v>
       </c>
       <c r="M13">
-        <v>2.5407536</v>
+        <v>2.7717312</v>
       </c>
       <c r="N13">
-        <v>48.8592464</v>
+        <v>48.6282688</v>
       </c>
       <c r="O13">
-        <v>12.6056855712</v>
+        <v>12.5460933504</v>
       </c>
       <c r="P13">
-        <v>36.2535608288</v>
+        <v>36.0821754496</v>
       </c>
       <c r="Q13">
-        <v>86.3535608288</v>
+        <v>86.18217544960001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07362898743061172</v>
+        <v>0.07387049024261541</v>
       </c>
       <c r="T13">
-        <v>0.6427017882358363</v>
+        <v>0.6482792203837277</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.23021831003211</v>
+        <v>18.5443667841961</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06948474341350155</v>
+        <v>0.06933420201375869</v>
       </c>
       <c r="C14">
-        <v>355.6102772295287</v>
+        <v>353.3966642980935</v>
       </c>
       <c r="D14">
-        <v>371.8142772295287</v>
+        <v>374.1926642980935</v>
       </c>
       <c r="E14">
-        <v>-94.396</v>
+        <v>-89.804</v>
       </c>
       <c r="F14">
-        <v>55.104</v>
+        <v>59.696</v>
       </c>
       <c r="G14">
         <v>38.9</v>
@@ -2435,28 +2435,28 @@
         <v>51.4</v>
       </c>
       <c r="M14">
-        <v>2.7717312</v>
+        <v>3.0027088</v>
       </c>
       <c r="N14">
-        <v>48.6282688</v>
+        <v>48.3972912</v>
       </c>
       <c r="O14">
-        <v>12.5460933504</v>
+        <v>12.4865011296</v>
       </c>
       <c r="P14">
-        <v>36.0821754496</v>
+        <v>35.9107900704</v>
       </c>
       <c r="Q14">
-        <v>86.18217544960001</v>
+        <v>86.01079007039999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07387049024261541</v>
+        <v>0.07411754484340079</v>
       </c>
       <c r="T14">
-        <v>0.6482792203837277</v>
+        <v>0.6539848693626047</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.5443667841961</v>
+        <v>17.11787703156563</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06933420201375869</v>
+        <v>0.06918366061401582</v>
       </c>
       <c r="C15">
-        <v>353.3966642980935</v>
+        <v>351.2136749481704</v>
       </c>
       <c r="D15">
-        <v>374.1926642980935</v>
+        <v>376.6016749481705</v>
       </c>
       <c r="E15">
-        <v>-89.804</v>
+        <v>-85.21199999999999</v>
       </c>
       <c r="F15">
-        <v>59.696</v>
+        <v>64.28800000000001</v>
       </c>
       <c r="G15">
         <v>38.9</v>
@@ -2517,28 +2517,28 @@
         <v>51.4</v>
       </c>
       <c r="M15">
-        <v>3.0027088</v>
+        <v>3.2336864</v>
       </c>
       <c r="N15">
-        <v>48.3972912</v>
+        <v>48.1663136</v>
       </c>
       <c r="O15">
-        <v>12.4865011296</v>
+        <v>12.4269089088</v>
       </c>
       <c r="P15">
-        <v>35.9107900704</v>
+        <v>35.73940469119999</v>
       </c>
       <c r="Q15">
-        <v>86.01079007039999</v>
+        <v>85.8394046912</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07411754484340079</v>
+        <v>0.07437034490001838</v>
       </c>
       <c r="T15">
-        <v>0.6539848693626047</v>
+        <v>0.6598232078526185</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.11787703156563</v>
+        <v>15.89517152931094</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06918366061401582</v>
+        <v>0.06903311921427292</v>
       </c>
       <c r="C16">
-        <v>351.2136749481704</v>
+        <v>349.0619044657544</v>
       </c>
       <c r="D16">
-        <v>376.6016749481705</v>
+        <v>379.0419044657544</v>
       </c>
       <c r="E16">
-        <v>-85.21199999999999</v>
+        <v>-80.61999999999999</v>
       </c>
       <c r="F16">
-        <v>64.28800000000001</v>
+        <v>68.88000000000001</v>
       </c>
       <c r="G16">
         <v>38.9</v>
@@ -2599,28 +2599,28 @@
         <v>51.4</v>
       </c>
       <c r="M16">
-        <v>3.2336864</v>
+        <v>3.464664</v>
       </c>
       <c r="N16">
-        <v>48.1663136</v>
+        <v>47.935336</v>
       </c>
       <c r="O16">
-        <v>12.4269089088</v>
+        <v>12.367316688</v>
       </c>
       <c r="P16">
-        <v>35.73940469119999</v>
+        <v>35.568019312</v>
       </c>
       <c r="Q16">
-        <v>85.8394046912</v>
+        <v>85.668019312</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07437034490001838</v>
+        <v>0.07462909319326227</v>
       </c>
       <c r="T16">
-        <v>0.6598232078526185</v>
+        <v>0.6657989190129856</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.89517152931094</v>
+        <v>14.83549342735688</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06903311921427292</v>
+        <v>0.06888257781453005</v>
       </c>
       <c r="C17">
-        <v>349.0619044657544</v>
+        <v>346.9419636663329</v>
       </c>
       <c r="D17">
-        <v>379.0419044657544</v>
+        <v>381.5139636663329</v>
       </c>
       <c r="E17">
-        <v>-80.62</v>
+        <v>-76.02800000000001</v>
       </c>
       <c r="F17">
-        <v>68.88</v>
+        <v>73.47199999999999</v>
       </c>
       <c r="G17">
         <v>38.9</v>
@@ -2681,28 +2681,28 @@
         <v>51.4</v>
       </c>
       <c r="M17">
-        <v>3.464664</v>
+        <v>3.6956416</v>
       </c>
       <c r="N17">
-        <v>47.935336</v>
+        <v>47.7043584</v>
       </c>
       <c r="O17">
-        <v>12.367316688</v>
+        <v>12.3077244672</v>
       </c>
       <c r="P17">
-        <v>35.568019312</v>
+        <v>35.3966339328</v>
       </c>
       <c r="Q17">
-        <v>85.668019312</v>
+        <v>85.49663393279999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07462909319326227</v>
+        <v>0.07489400216015484</v>
       </c>
       <c r="T17">
-        <v>0.6657989190129856</v>
+        <v>0.6719169090105043</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.83549342735688</v>
+        <v>13.90827508814708</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06888257781453005</v>
+        <v>0.06873203641478719</v>
       </c>
       <c r="C18">
-        <v>346.9419636663329</v>
+        <v>344.8544794046188</v>
       </c>
       <c r="D18">
-        <v>381.5139636663329</v>
+        <v>384.0184794046188</v>
       </c>
       <c r="E18">
-        <v>-76.02800000000001</v>
+        <v>-71.43599999999999</v>
       </c>
       <c r="F18">
-        <v>73.47199999999999</v>
+        <v>78.06400000000001</v>
       </c>
       <c r="G18">
         <v>38.9</v>
@@ -2763,28 +2763,28 @@
         <v>51.4</v>
       </c>
       <c r="M18">
-        <v>3.6956416</v>
+        <v>3.9266192</v>
       </c>
       <c r="N18">
-        <v>47.7043584</v>
+        <v>47.4733808</v>
       </c>
       <c r="O18">
-        <v>12.3077244672</v>
+        <v>12.2481322464</v>
       </c>
       <c r="P18">
-        <v>35.3966339328</v>
+        <v>35.2252485536</v>
       </c>
       <c r="Q18">
-        <v>85.49663393279999</v>
+        <v>85.32524855360001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07489400216015484</v>
+        <v>0.07516529447564722</v>
       </c>
       <c r="T18">
-        <v>0.6719169090105043</v>
+        <v>0.6781823204537464</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.90827508814708</v>
+        <v>13.09014125943254</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06873203641478719</v>
+        <v>0.06878183501504431</v>
       </c>
       <c r="C19">
-        <v>344.8544794046188</v>
+        <v>339.4303620939383</v>
       </c>
       <c r="D19">
-        <v>384.0184794046188</v>
+        <v>383.1863620939383</v>
       </c>
       <c r="E19">
-        <v>-71.43599999999999</v>
+        <v>-66.84399999999999</v>
       </c>
       <c r="F19">
-        <v>78.06400000000001</v>
+        <v>82.65600000000001</v>
       </c>
       <c r="G19">
         <v>38.9</v>
@@ -2845,45 +2845,45 @@
         <v>51.4</v>
       </c>
       <c r="M19">
-        <v>3.9266192</v>
+        <v>4.2815808</v>
       </c>
       <c r="N19">
-        <v>47.4733808</v>
+        <v>47.1184192</v>
       </c>
       <c r="O19">
-        <v>12.2481322464</v>
+        <v>12.1565521536</v>
       </c>
       <c r="P19">
-        <v>35.2252485536</v>
+        <v>34.9618670464</v>
       </c>
       <c r="Q19">
-        <v>85.32524855360001</v>
+        <v>85.06186704640001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07516529447564722</v>
+        <v>0.07544320367688331</v>
       </c>
       <c r="T19">
-        <v>0.6781823204537464</v>
+        <v>0.6846005468102381</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.09014125943254</v>
+        <v>12.0049118306958</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06878183501504431</v>
+        <v>0.06864242361530146</v>
       </c>
       <c r="C20">
-        <v>339.4303620939383</v>
+        <v>337.1770170458631</v>
       </c>
       <c r="D20">
-        <v>383.1863620939383</v>
+        <v>385.5250170458631</v>
       </c>
       <c r="E20">
-        <v>-66.84400000000001</v>
+        <v>-62.252</v>
       </c>
       <c r="F20">
-        <v>82.65599999999999</v>
+        <v>87.248</v>
       </c>
       <c r="G20">
         <v>38.9</v>
@@ -2927,28 +2927,28 @@
         <v>51.4</v>
       </c>
       <c r="M20">
-        <v>4.2815808</v>
+        <v>4.519446400000001</v>
       </c>
       <c r="N20">
-        <v>47.1184192</v>
+        <v>46.8805536</v>
       </c>
       <c r="O20">
-        <v>12.1565521536</v>
+        <v>12.0951828288</v>
       </c>
       <c r="P20">
-        <v>34.9618670464</v>
+        <v>34.7853707712</v>
       </c>
       <c r="Q20">
-        <v>85.06186704640001</v>
+        <v>84.8853707712</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07544320367688331</v>
+        <v>0.0757279748337055</v>
       </c>
       <c r="T20">
-        <v>0.6846005468102381</v>
+        <v>0.6911772478915816</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.0049118306958</v>
+        <v>11.37307436592234</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06864242361530146</v>
+        <v>0.06850301221555857</v>
       </c>
       <c r="C21">
-        <v>337.1770170458631</v>
+        <v>334.9523937512956</v>
       </c>
       <c r="D21">
-        <v>385.5250170458631</v>
+        <v>387.8923937512956</v>
       </c>
       <c r="E21">
-        <v>-62.252</v>
+        <v>-57.66</v>
       </c>
       <c r="F21">
-        <v>87.248</v>
+        <v>91.84</v>
       </c>
       <c r="G21">
         <v>38.9</v>
@@ -3009,28 +3009,28 @@
         <v>51.4</v>
       </c>
       <c r="M21">
-        <v>4.519446400000001</v>
+        <v>4.757312</v>
       </c>
       <c r="N21">
-        <v>46.8805536</v>
+        <v>46.642688</v>
       </c>
       <c r="O21">
-        <v>12.0951828288</v>
+        <v>12.033813504</v>
       </c>
       <c r="P21">
-        <v>34.7853707712</v>
+        <v>34.608874496</v>
       </c>
       <c r="Q21">
-        <v>84.8853707712</v>
+        <v>84.70887449599999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0757279748337055</v>
+        <v>0.07601986526944821</v>
       </c>
       <c r="T21">
-        <v>0.6911772478915816</v>
+        <v>0.6979183664999586</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.37307436592234</v>
+        <v>10.80442064762622</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06850301221555857</v>
+        <v>0.06836360081581572</v>
       </c>
       <c r="C22">
-        <v>334.9523937512956</v>
+        <v>332.7570245906682</v>
       </c>
       <c r="D22">
-        <v>387.8923937512956</v>
+        <v>390.2890245906682</v>
       </c>
       <c r="E22">
-        <v>-57.66</v>
+        <v>-53.068</v>
       </c>
       <c r="F22">
-        <v>91.84</v>
+        <v>96.432</v>
       </c>
       <c r="G22">
         <v>38.9</v>
@@ -3091,28 +3091,28 @@
         <v>51.4</v>
       </c>
       <c r="M22">
-        <v>4.757312</v>
+        <v>4.9951776</v>
       </c>
       <c r="N22">
-        <v>46.642688</v>
+        <v>46.4048224</v>
       </c>
       <c r="O22">
-        <v>12.033813504</v>
+        <v>11.9724441792</v>
       </c>
       <c r="P22">
-        <v>34.608874496</v>
+        <v>34.4323782208</v>
       </c>
       <c r="Q22">
-        <v>84.70887449599999</v>
+        <v>84.53237822080001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07601986526944821</v>
+        <v>0.07631914533647557</v>
       </c>
       <c r="T22">
-        <v>0.6979183664999586</v>
+        <v>0.7048301463389276</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.80442064762622</v>
+        <v>10.28992442631069</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06836360081581569</v>
+        <v>0.06822418941607283</v>
       </c>
       <c r="C23">
-        <v>332.7570245906686</v>
+        <v>330.5914551836719</v>
       </c>
       <c r="D23">
-        <v>390.2890245906686</v>
+        <v>392.7154551836719</v>
       </c>
       <c r="E23">
-        <v>-53.06800000000001</v>
+        <v>-48.476</v>
       </c>
       <c r="F23">
-        <v>96.43199999999999</v>
+        <v>101.024</v>
       </c>
       <c r="G23">
         <v>38.9</v>
@@ -3173,28 +3173,28 @@
         <v>51.4</v>
       </c>
       <c r="M23">
-        <v>4.995177599999999</v>
+        <v>5.2330432</v>
       </c>
       <c r="N23">
-        <v>46.4048224</v>
+        <v>46.1669568</v>
       </c>
       <c r="O23">
-        <v>11.9724441792</v>
+        <v>11.9110748544</v>
       </c>
       <c r="P23">
-        <v>34.4323782208</v>
+        <v>34.2558819456</v>
       </c>
       <c r="Q23">
-        <v>84.53237822080001</v>
+        <v>84.3558819456</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07631914533647556</v>
+        <v>0.07662609925137542</v>
       </c>
       <c r="T23">
-        <v>0.7048301463389275</v>
+        <v>0.7119191513019726</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.28992442631069</v>
+        <v>9.822200588751112</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06822418941607283</v>
+        <v>0.06837490001632995</v>
       </c>
       <c r="C24">
-        <v>330.5914551836719</v>
+        <v>323.377676928257</v>
       </c>
       <c r="D24">
-        <v>392.7154551836719</v>
+        <v>390.093676928257</v>
       </c>
       <c r="E24">
-        <v>-48.476</v>
+        <v>-43.884</v>
       </c>
       <c r="F24">
-        <v>101.024</v>
+        <v>105.616</v>
       </c>
       <c r="G24">
         <v>38.9</v>
@@ -3255,45 +3255,45 @@
         <v>51.4</v>
       </c>
       <c r="M24">
-        <v>5.2330432</v>
+        <v>5.650456</v>
       </c>
       <c r="N24">
-        <v>46.1669568</v>
+        <v>45.749544</v>
       </c>
       <c r="O24">
-        <v>11.9110748544</v>
+        <v>11.803382352</v>
       </c>
       <c r="P24">
-        <v>34.2558819456</v>
+        <v>33.946161648</v>
       </c>
       <c r="Q24">
-        <v>84.3558819456</v>
+        <v>84.04616164800001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07662609925137542</v>
+        <v>0.0769410259952337</v>
       </c>
       <c r="T24">
-        <v>0.7119191513019726</v>
+        <v>0.7191922862640577</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.822200588751112</v>
+        <v>9.0966109637877</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06837490001632995</v>
+        <v>0.06824810261658708</v>
       </c>
       <c r="C25">
-        <v>323.377676928257</v>
+        <v>320.9891087610254</v>
       </c>
       <c r="D25">
-        <v>390.093676928257</v>
+        <v>392.2971087610254</v>
       </c>
       <c r="E25">
-        <v>-43.884</v>
+        <v>-39.29199999999999</v>
       </c>
       <c r="F25">
-        <v>105.616</v>
+        <v>110.208</v>
       </c>
       <c r="G25">
         <v>38.9</v>
@@ -3337,28 +3337,28 @@
         <v>51.4</v>
       </c>
       <c r="M25">
-        <v>5.650456</v>
+        <v>5.896128000000001</v>
       </c>
       <c r="N25">
-        <v>45.749544</v>
+        <v>45.503872</v>
       </c>
       <c r="O25">
-        <v>11.803382352</v>
+        <v>11.739998976</v>
       </c>
       <c r="P25">
-        <v>33.946161648</v>
+        <v>33.763873024</v>
       </c>
       <c r="Q25">
-        <v>84.04616164800001</v>
+        <v>83.863873024</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0769410259952337</v>
+        <v>0.07726424028498299</v>
       </c>
       <c r="T25">
-        <v>0.7191922862640577</v>
+        <v>0.7266568195146188</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.0966109637877</v>
+        <v>8.717585506963212</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06824810261658708</v>
+        <v>0.0681213052168442</v>
       </c>
       <c r="C26">
-        <v>320.9891087610254</v>
+        <v>318.6255740247865</v>
       </c>
       <c r="D26">
-        <v>392.2971087610254</v>
+        <v>394.5255740247865</v>
       </c>
       <c r="E26">
-        <v>-39.292</v>
+        <v>-34.7</v>
       </c>
       <c r="F26">
-        <v>110.208</v>
+        <v>114.8</v>
       </c>
       <c r="G26">
         <v>38.9</v>
@@ -3419,28 +3419,28 @@
         <v>51.4</v>
       </c>
       <c r="M26">
-        <v>5.896128</v>
+        <v>6.1418</v>
       </c>
       <c r="N26">
-        <v>45.503872</v>
+        <v>45.2582</v>
       </c>
       <c r="O26">
-        <v>11.739998976</v>
+        <v>11.6766156</v>
       </c>
       <c r="P26">
-        <v>33.763873024</v>
+        <v>33.5815844</v>
       </c>
       <c r="Q26">
-        <v>83.863873024</v>
+        <v>83.68158439999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07726424028498299</v>
+        <v>0.07759607362245893</v>
       </c>
       <c r="T26">
-        <v>0.7266568195146188</v>
+        <v>0.7343204069851949</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.717585506963214</v>
+        <v>8.368882086684685</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0681213052168442</v>
+        <v>0.06799450781710133</v>
       </c>
       <c r="C27">
-        <v>318.6255740247865</v>
+        <v>316.2875017681116</v>
       </c>
       <c r="D27">
-        <v>394.5255740247865</v>
+        <v>396.7795017681116</v>
       </c>
       <c r="E27">
-        <v>-34.7</v>
+        <v>-30.108</v>
       </c>
       <c r="F27">
-        <v>114.8</v>
+        <v>119.392</v>
       </c>
       <c r="G27">
         <v>38.9</v>
@@ -3501,28 +3501,28 @@
         <v>51.4</v>
       </c>
       <c r="M27">
-        <v>6.1418</v>
+        <v>6.387472</v>
       </c>
       <c r="N27">
-        <v>45.2582</v>
+        <v>45.012528</v>
       </c>
       <c r="O27">
-        <v>11.6766156</v>
+        <v>11.613232224</v>
       </c>
       <c r="P27">
-        <v>33.5815844</v>
+        <v>33.399295776</v>
       </c>
       <c r="Q27">
-        <v>83.68158439999999</v>
+        <v>83.499295776</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07759607362245893</v>
+        <v>0.07793687542851531</v>
       </c>
       <c r="T27">
-        <v>0.7343204069851949</v>
+        <v>0.742191118441462</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.368882086684685</v>
+        <v>8.047002006427583</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06799450781710133</v>
+        <v>0.06786771041735846</v>
       </c>
       <c r="C28">
-        <v>316.2875017681116</v>
+        <v>313.9753309005389</v>
       </c>
       <c r="D28">
-        <v>396.7795017681116</v>
+        <v>399.0593309005389</v>
       </c>
       <c r="E28">
-        <v>-30.108</v>
+        <v>-25.51599999999999</v>
       </c>
       <c r="F28">
-        <v>119.392</v>
+        <v>123.984</v>
       </c>
       <c r="G28">
         <v>38.9</v>
@@ -3583,28 +3583,28 @@
         <v>51.4</v>
       </c>
       <c r="M28">
-        <v>6.387472</v>
+        <v>6.633144000000001</v>
       </c>
       <c r="N28">
-        <v>45.012528</v>
+        <v>44.766856</v>
       </c>
       <c r="O28">
-        <v>11.613232224</v>
+        <v>11.549848848</v>
       </c>
       <c r="P28">
-        <v>33.399295776</v>
+        <v>33.21700715199999</v>
       </c>
       <c r="Q28">
-        <v>83.499295776</v>
+        <v>83.317007152</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07793687542851531</v>
+        <v>0.07828701427035406</v>
       </c>
       <c r="T28">
-        <v>0.742191118441462</v>
+        <v>0.7502774658280381</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.047002006427583</v>
+        <v>7.748964895078411</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06786771041735846</v>
+        <v>0.06790712101761558</v>
       </c>
       <c r="C29">
-        <v>313.9753309005389</v>
+        <v>308.6719235781444</v>
       </c>
       <c r="D29">
-        <v>399.0593309005389</v>
+        <v>398.3479235781444</v>
       </c>
       <c r="E29">
-        <v>-25.51599999999999</v>
+        <v>-20.92399999999998</v>
       </c>
       <c r="F29">
-        <v>123.984</v>
+        <v>128.576</v>
       </c>
       <c r="G29">
         <v>38.9</v>
@@ -3665,45 +3665,45 @@
         <v>51.4</v>
       </c>
       <c r="M29">
-        <v>6.633144000000001</v>
+        <v>6.981676800000002</v>
       </c>
       <c r="N29">
-        <v>44.766856</v>
+        <v>44.4183232</v>
       </c>
       <c r="O29">
-        <v>11.549848848</v>
+        <v>11.4599273856</v>
       </c>
       <c r="P29">
-        <v>33.21700715199999</v>
+        <v>32.9583958144</v>
       </c>
       <c r="Q29">
-        <v>83.317007152</v>
+        <v>83.0583958144</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07828701427035406</v>
+        <v>0.07864687919113275</v>
       </c>
       <c r="T29">
-        <v>0.7502774658280381</v>
+        <v>0.7585884339753522</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.748964895078411</v>
+        <v>7.362128249763723</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06790712101761558</v>
+        <v>0.06778625961787271</v>
       </c>
       <c r="C30">
-        <v>308.6719235781444</v>
+        <v>306.2696952112048</v>
       </c>
       <c r="D30">
-        <v>398.3479235781444</v>
+        <v>400.5376952112048</v>
       </c>
       <c r="E30">
-        <v>-20.92399999999998</v>
+        <v>-16.33199999999999</v>
       </c>
       <c r="F30">
-        <v>128.576</v>
+        <v>133.168</v>
       </c>
       <c r="G30">
         <v>38.9</v>
@@ -3747,28 +3747,28 @@
         <v>51.4</v>
       </c>
       <c r="M30">
-        <v>6.981676800000002</v>
+        <v>7.231022400000001</v>
       </c>
       <c r="N30">
-        <v>44.4183232</v>
+        <v>44.1689776</v>
       </c>
       <c r="O30">
-        <v>11.4599273856</v>
+        <v>11.3955962208</v>
       </c>
       <c r="P30">
-        <v>32.9583958144</v>
+        <v>32.7733813792</v>
       </c>
       <c r="Q30">
-        <v>83.0583958144</v>
+        <v>82.8733813792</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07864687919113275</v>
+        <v>0.07901688115193339</v>
       </c>
       <c r="T30">
-        <v>0.7585884339753522</v>
+        <v>0.767133513901464</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.362128249763723</v>
+        <v>7.108261758392561</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0677862596178727</v>
+        <v>0.06766539821812982</v>
       </c>
       <c r="C31">
-        <v>306.2696952112051</v>
+        <v>303.8916748520091</v>
       </c>
       <c r="D31">
-        <v>400.5376952112051</v>
+        <v>402.7516748520091</v>
       </c>
       <c r="E31">
-        <v>-16.33200000000002</v>
+        <v>-11.74000000000001</v>
       </c>
       <c r="F31">
-        <v>133.168</v>
+        <v>137.76</v>
       </c>
       <c r="G31">
         <v>38.9</v>
@@ -3829,28 +3829,28 @@
         <v>51.4</v>
       </c>
       <c r="M31">
-        <v>7.231022399999999</v>
+        <v>7.480367999999999</v>
       </c>
       <c r="N31">
-        <v>44.1689776</v>
+        <v>43.919632</v>
       </c>
       <c r="O31">
-        <v>11.3955962208</v>
+        <v>11.331265056</v>
       </c>
       <c r="P31">
-        <v>32.7733813792</v>
+        <v>32.588366944</v>
       </c>
       <c r="Q31">
-        <v>82.8733813792</v>
+        <v>82.68836694399999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07901688115193339</v>
+        <v>0.07939745459732833</v>
       </c>
       <c r="T31">
-        <v>0.767133513901464</v>
+        <v>0.7759227389683219</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.108261758392563</v>
+        <v>6.871319699779477</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06766539821812982</v>
+        <v>0.06754453681838697</v>
       </c>
       <c r="C32">
-        <v>303.8916748520091</v>
+        <v>301.5382661624586</v>
       </c>
       <c r="D32">
-        <v>402.7516748520091</v>
+        <v>404.9902661624586</v>
       </c>
       <c r="E32">
-        <v>-11.74000000000001</v>
+        <v>-7.147999999999996</v>
       </c>
       <c r="F32">
-        <v>137.76</v>
+        <v>142.352</v>
       </c>
       <c r="G32">
         <v>38.9</v>
@@ -3911,28 +3911,28 @@
         <v>51.4</v>
       </c>
       <c r="M32">
-        <v>7.480367999999999</v>
+        <v>7.7297136</v>
       </c>
       <c r="N32">
-        <v>43.919632</v>
+        <v>43.67028639999999</v>
       </c>
       <c r="O32">
-        <v>11.331265056</v>
+        <v>11.2669338912</v>
       </c>
       <c r="P32">
-        <v>32.588366944</v>
+        <v>32.4033525088</v>
       </c>
       <c r="Q32">
-        <v>82.68836694399999</v>
+        <v>82.50335250879999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07939745459732833</v>
+        <v>0.07978905915708256</v>
       </c>
       <c r="T32">
-        <v>0.7759227389683219</v>
+        <v>0.7849667241820452</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.871319699779477</v>
+        <v>6.649664225593041</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06754453681838697</v>
+        <v>0.06742367541864409</v>
       </c>
       <c r="C33">
-        <v>301.5382661624586</v>
+        <v>299.2098818292213</v>
       </c>
       <c r="D33">
-        <v>404.9902661624586</v>
+        <v>407.2538818292214</v>
       </c>
       <c r="E33">
-        <v>-7.147999999999996</v>
+        <v>-2.556000000000012</v>
       </c>
       <c r="F33">
-        <v>142.352</v>
+        <v>146.944</v>
       </c>
       <c r="G33">
         <v>38.9</v>
@@ -3993,28 +3993,28 @@
         <v>51.4</v>
       </c>
       <c r="M33">
-        <v>7.7297136</v>
+        <v>7.979059199999999</v>
       </c>
       <c r="N33">
-        <v>43.67028639999999</v>
+        <v>43.4209408</v>
       </c>
       <c r="O33">
-        <v>11.2669338912</v>
+        <v>11.2026027264</v>
       </c>
       <c r="P33">
-        <v>32.4033525088</v>
+        <v>32.21833807359999</v>
       </c>
       <c r="Q33">
-        <v>82.50335250879999</v>
+        <v>82.31833807359999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07978905915708256</v>
+        <v>0.08019218149800603</v>
       </c>
       <c r="T33">
-        <v>0.7849667241820452</v>
+        <v>0.7942767089608779</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.649664225593041</v>
+        <v>6.441862218543259</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06742367541864409</v>
+        <v>0.06730281401890122</v>
       </c>
       <c r="C34">
-        <v>299.2098818292213</v>
+        <v>296.9069438173562</v>
       </c>
       <c r="D34">
-        <v>407.2538818292214</v>
+        <v>409.5429438173562</v>
       </c>
       <c r="E34">
-        <v>-2.556000000000012</v>
+        <v>2.036000000000001</v>
       </c>
       <c r="F34">
-        <v>146.944</v>
+        <v>151.536</v>
       </c>
       <c r="G34">
         <v>38.9</v>
@@ -4075,28 +4075,28 @@
         <v>51.4</v>
       </c>
       <c r="M34">
-        <v>7.979059199999999</v>
+        <v>8.2284048</v>
       </c>
       <c r="N34">
-        <v>43.4209408</v>
+        <v>43.1715952</v>
       </c>
       <c r="O34">
-        <v>11.2026027264</v>
+        <v>11.1382715616</v>
       </c>
       <c r="P34">
-        <v>32.21833807359999</v>
+        <v>32.0333236384</v>
       </c>
       <c r="Q34">
-        <v>82.31833807359999</v>
+        <v>82.1333236384</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08019218149800603</v>
+        <v>0.0806073373416436</v>
       </c>
       <c r="T34">
-        <v>0.7942767089608779</v>
+        <v>0.8038646037331086</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.441862218543259</v>
+        <v>6.246654272526796</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06730281401890122</v>
+        <v>0.06743423261915833</v>
       </c>
       <c r="C35">
-        <v>296.9069438173562</v>
+        <v>289.8271476764386</v>
       </c>
       <c r="D35">
-        <v>409.5429438173562</v>
+        <v>407.0551476764387</v>
       </c>
       <c r="E35">
-        <v>2.036000000000001</v>
+        <v>6.628000000000014</v>
       </c>
       <c r="F35">
-        <v>151.536</v>
+        <v>156.128</v>
       </c>
       <c r="G35">
         <v>38.9</v>
@@ -4157,45 +4157,45 @@
         <v>51.4</v>
       </c>
       <c r="M35">
-        <v>8.2284048</v>
+        <v>8.6338784</v>
       </c>
       <c r="N35">
-        <v>43.1715952</v>
+        <v>42.7661216</v>
       </c>
       <c r="O35">
-        <v>11.1382715616</v>
+        <v>11.0336593728</v>
       </c>
       <c r="P35">
-        <v>32.0333236384</v>
+        <v>31.7324622272</v>
       </c>
       <c r="Q35">
-        <v>82.1333236384</v>
+        <v>81.8324622272</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0806073373416436</v>
+        <v>0.08103507366539142</v>
       </c>
       <c r="T35">
-        <v>0.8038646037331086</v>
+        <v>0.8137430407711645</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.246654272526796</v>
+        <v>5.95329209176724</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06743423261915833</v>
+        <v>0.06732079121941546</v>
       </c>
       <c r="C36">
-        <v>289.8271476764386</v>
+        <v>287.3808357812187</v>
       </c>
       <c r="D36">
-        <v>407.0551476764387</v>
+        <v>409.2008357812188</v>
       </c>
       <c r="E36">
-        <v>6.628000000000014</v>
+        <v>11.22</v>
       </c>
       <c r="F36">
-        <v>156.128</v>
+        <v>160.72</v>
       </c>
       <c r="G36">
         <v>38.9</v>
@@ -4239,28 +4239,28 @@
         <v>51.4</v>
       </c>
       <c r="M36">
-        <v>8.6338784</v>
+        <v>8.887816000000001</v>
       </c>
       <c r="N36">
-        <v>42.7661216</v>
+        <v>42.512184</v>
       </c>
       <c r="O36">
-        <v>11.0336593728</v>
+        <v>10.968143472</v>
       </c>
       <c r="P36">
-        <v>31.7324622272</v>
+        <v>31.544040528</v>
       </c>
       <c r="Q36">
-        <v>81.8324622272</v>
+        <v>81.644040528</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08103507366539142</v>
+        <v>0.08147597110679303</v>
       </c>
       <c r="T36">
-        <v>0.8137430407711645</v>
+        <v>0.8239254297180838</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.95329209176724</v>
+        <v>5.783198032002462</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06732079121941546</v>
+        <v>0.06720734981967259</v>
       </c>
       <c r="C37">
-        <v>287.3808357812187</v>
+        <v>284.9572646609259</v>
       </c>
       <c r="D37">
-        <v>409.2008357812188</v>
+        <v>411.369264660926</v>
       </c>
       <c r="E37">
-        <v>11.22</v>
+        <v>15.81200000000001</v>
       </c>
       <c r="F37">
-        <v>160.72</v>
+        <v>165.312</v>
       </c>
       <c r="G37">
         <v>38.9</v>
@@ -4321,28 +4321,28 @@
         <v>51.4</v>
       </c>
       <c r="M37">
-        <v>8.887816000000001</v>
+        <v>9.141753600000001</v>
       </c>
       <c r="N37">
-        <v>42.512184</v>
+        <v>42.2582464</v>
       </c>
       <c r="O37">
-        <v>10.968143472</v>
+        <v>10.9026275712</v>
       </c>
       <c r="P37">
-        <v>31.544040528</v>
+        <v>31.3556188288</v>
       </c>
       <c r="Q37">
-        <v>81.644040528</v>
+        <v>81.4556188288</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08147597110679303</v>
+        <v>0.08193064659323843</v>
       </c>
       <c r="T37">
-        <v>0.8239254297180838</v>
+        <v>0.8344260183195942</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.783198032002462</v>
+        <v>5.622553642224616</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06720734981967259</v>
+        <v>0.06709390841992972</v>
       </c>
       <c r="C38">
-        <v>284.9572646609259</v>
+        <v>282.5567977639168</v>
       </c>
       <c r="D38">
-        <v>411.369264660926</v>
+        <v>413.5607977639168</v>
       </c>
       <c r="E38">
-        <v>15.81199999999998</v>
+        <v>20.404</v>
       </c>
       <c r="F38">
-        <v>165.312</v>
+        <v>169.904</v>
       </c>
       <c r="G38">
         <v>38.9</v>
@@ -4403,28 +4403,28 @@
         <v>51.4</v>
       </c>
       <c r="M38">
-        <v>9.141753599999999</v>
+        <v>9.3956912</v>
       </c>
       <c r="N38">
-        <v>42.2582464</v>
+        <v>42.0043088</v>
       </c>
       <c r="O38">
-        <v>10.9026275712</v>
+        <v>10.8371116704</v>
       </c>
       <c r="P38">
-        <v>31.3556188288</v>
+        <v>31.1671971296</v>
       </c>
       <c r="Q38">
-        <v>81.4556188288</v>
+        <v>81.26719712959999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08193064659323843</v>
+        <v>0.08239975622211068</v>
       </c>
       <c r="T38">
-        <v>0.8344260183195942</v>
+        <v>0.8452599589402002</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.622553642224617</v>
+        <v>5.470592732975303</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06709390841992972</v>
+        <v>0.06698046702018685</v>
       </c>
       <c r="C39">
-        <v>282.5567977639168</v>
+        <v>280.1798063249839</v>
       </c>
       <c r="D39">
-        <v>413.5607977639168</v>
+        <v>415.775806324984</v>
       </c>
       <c r="E39">
-        <v>20.404</v>
+        <v>24.99600000000001</v>
       </c>
       <c r="F39">
-        <v>169.904</v>
+        <v>174.496</v>
       </c>
       <c r="G39">
         <v>38.9</v>
@@ -4485,28 +4485,28 @@
         <v>51.4</v>
       </c>
       <c r="M39">
-        <v>9.3956912</v>
+        <v>9.6496288</v>
       </c>
       <c r="N39">
-        <v>42.0043088</v>
+        <v>41.7503712</v>
       </c>
       <c r="O39">
-        <v>10.8371116704</v>
+        <v>10.7715957696</v>
       </c>
       <c r="P39">
-        <v>31.1671971296</v>
+        <v>30.9787754304</v>
       </c>
       <c r="Q39">
-        <v>81.26719712959999</v>
+        <v>81.0787754304</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08239975622211068</v>
+        <v>0.08288399841965621</v>
       </c>
       <c r="T39">
-        <v>0.8452599589402002</v>
+        <v>0.8564433815163096</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.470592732975303</v>
+        <v>5.326629766318058</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06698046702018685</v>
+        <v>0.06686702562044397</v>
       </c>
       <c r="C40">
-        <v>280.1798063249839</v>
+        <v>277.8266695749988</v>
       </c>
       <c r="D40">
-        <v>415.775806324984</v>
+        <v>418.0146695749988</v>
       </c>
       <c r="E40">
-        <v>24.99600000000001</v>
+        <v>29.58799999999999</v>
       </c>
       <c r="F40">
-        <v>174.496</v>
+        <v>179.088</v>
       </c>
       <c r="G40">
         <v>38.9</v>
@@ -4567,28 +4567,28 @@
         <v>51.4</v>
       </c>
       <c r="M40">
-        <v>9.6496288</v>
+        <v>9.903566400000001</v>
       </c>
       <c r="N40">
-        <v>41.7503712</v>
+        <v>41.4964336</v>
       </c>
       <c r="O40">
-        <v>10.7715957696</v>
+        <v>10.7060798688</v>
       </c>
       <c r="P40">
-        <v>30.9787754304</v>
+        <v>30.7903537312</v>
       </c>
       <c r="Q40">
-        <v>81.0787754304</v>
+        <v>80.89035373119999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08288399841965621</v>
+        <v>0.0833841174105639</v>
       </c>
       <c r="T40">
-        <v>0.8564433815163096</v>
+        <v>0.8679934736850783</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.326629766318058</v>
+        <v>5.190049515899645</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06686702562044397</v>
+        <v>0.0667535842207011</v>
       </c>
       <c r="C41">
-        <v>277.8266695749988</v>
+        <v>275.4977749573607</v>
       </c>
       <c r="D41">
-        <v>418.0146695749988</v>
+        <v>420.2777749573607</v>
       </c>
       <c r="E41">
-        <v>29.58799999999999</v>
+        <v>34.18000000000001</v>
       </c>
       <c r="F41">
-        <v>179.088</v>
+        <v>183.68</v>
       </c>
       <c r="G41">
         <v>38.9</v>
@@ -4649,28 +4649,28 @@
         <v>51.4</v>
       </c>
       <c r="M41">
-        <v>9.903566400000001</v>
+        <v>10.157504</v>
       </c>
       <c r="N41">
-        <v>41.4964336</v>
+        <v>41.242496</v>
       </c>
       <c r="O41">
-        <v>10.7060798688</v>
+        <v>10.640563968</v>
       </c>
       <c r="P41">
-        <v>30.7903537312</v>
+        <v>30.601932032</v>
       </c>
       <c r="Q41">
-        <v>80.89035373119999</v>
+        <v>80.701932032</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0833841174105639</v>
+        <v>0.08390090703450184</v>
       </c>
       <c r="T41">
-        <v>0.8679934736850783</v>
+        <v>0.8799285689261395</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.190049515899645</v>
+        <v>5.060298278002154</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0667535842207011</v>
+        <v>0.06664014282095823</v>
       </c>
       <c r="C42">
-        <v>275.4977749573607</v>
+        <v>273.1935183515199</v>
       </c>
       <c r="D42">
-        <v>420.2777749573607</v>
+        <v>422.5655183515199</v>
       </c>
       <c r="E42">
-        <v>34.18000000000001</v>
+        <v>38.77200000000002</v>
       </c>
       <c r="F42">
-        <v>183.68</v>
+        <v>188.272</v>
       </c>
       <c r="G42">
         <v>38.9</v>
@@ -4731,28 +4731,28 @@
         <v>51.4</v>
       </c>
       <c r="M42">
-        <v>10.157504</v>
+        <v>10.4114416</v>
       </c>
       <c r="N42">
-        <v>41.242496</v>
+        <v>40.9885584</v>
       </c>
       <c r="O42">
-        <v>10.640563968</v>
+        <v>10.5750480672</v>
       </c>
       <c r="P42">
-        <v>30.601932032</v>
+        <v>30.41351033279999</v>
       </c>
       <c r="Q42">
-        <v>80.701932032</v>
+        <v>80.5135103328</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08390090703450184</v>
+        <v>0.08443521495077666</v>
       </c>
       <c r="T42">
-        <v>0.8799285689261395</v>
+        <v>0.8922682436668974</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.060298278002154</v>
+        <v>4.936876368782589</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06664014282095823</v>
+        <v>0.06652670142121536</v>
       </c>
       <c r="C43">
-        <v>273.1935183515199</v>
+        <v>270.9143043038374</v>
       </c>
       <c r="D43">
-        <v>422.5655183515199</v>
+        <v>424.8783043038375</v>
       </c>
       <c r="E43">
-        <v>38.77200000000002</v>
+        <v>43.364</v>
       </c>
       <c r="F43">
-        <v>188.272</v>
+        <v>192.864</v>
       </c>
       <c r="G43">
         <v>38.9</v>
@@ -4813,28 +4813,28 @@
         <v>51.4</v>
       </c>
       <c r="M43">
-        <v>10.4114416</v>
+        <v>10.6653792</v>
       </c>
       <c r="N43">
-        <v>40.9885584</v>
+        <v>40.7346208</v>
       </c>
       <c r="O43">
-        <v>10.5750480672</v>
+        <v>10.5095321664</v>
       </c>
       <c r="P43">
-        <v>30.41351033279999</v>
+        <v>30.2250886336</v>
       </c>
       <c r="Q43">
-        <v>80.5135103328</v>
+        <v>80.3250886336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08443521495077666</v>
+        <v>0.08498794727795751</v>
       </c>
       <c r="T43">
-        <v>0.8922682436668974</v>
+        <v>0.9050334244331988</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.936876368782589</v>
+        <v>4.819331693335386</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06652670142121536</v>
+        <v>0.06641326002147248</v>
       </c>
       <c r="C44">
-        <v>270.9143043038375</v>
+        <v>268.6605462660697</v>
       </c>
       <c r="D44">
-        <v>424.8783043038375</v>
+        <v>427.2165462660697</v>
       </c>
       <c r="E44">
-        <v>43.36399999999998</v>
+        <v>47.95599999999999</v>
       </c>
       <c r="F44">
-        <v>192.864</v>
+        <v>197.456</v>
       </c>
       <c r="G44">
         <v>38.9</v>
@@ -4895,28 +4895,28 @@
         <v>51.4</v>
       </c>
       <c r="M44">
-        <v>10.6653792</v>
+        <v>10.9193168</v>
       </c>
       <c r="N44">
-        <v>40.7346208</v>
+        <v>40.4806832</v>
       </c>
       <c r="O44">
-        <v>10.5095321664</v>
+        <v>10.4440162656</v>
       </c>
       <c r="P44">
-        <v>30.2250886336</v>
+        <v>30.0366669344</v>
       </c>
       <c r="Q44">
-        <v>80.3250886336</v>
+        <v>80.13666693440001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08498794727795751</v>
+        <v>0.08556007372188154</v>
       </c>
       <c r="T44">
-        <v>0.9050334244331988</v>
+        <v>0.9182465062790195</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.819331693335386</v>
+        <v>4.707254212095028</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06641326002147248</v>
+        <v>0.06629981862172961</v>
       </c>
       <c r="C45">
-        <v>268.6605462660697</v>
+        <v>266.432666841769</v>
       </c>
       <c r="D45">
-        <v>427.2165462660697</v>
+        <v>429.5806668417691</v>
       </c>
       <c r="E45">
-        <v>47.95599999999999</v>
+        <v>52.548</v>
       </c>
       <c r="F45">
-        <v>197.456</v>
+        <v>202.048</v>
       </c>
       <c r="G45">
         <v>38.9</v>
@@ -4977,28 +4977,28 @@
         <v>51.4</v>
       </c>
       <c r="M45">
-        <v>10.9193168</v>
+        <v>11.1732544</v>
       </c>
       <c r="N45">
-        <v>40.4806832</v>
+        <v>40.2267456</v>
       </c>
       <c r="O45">
-        <v>10.4440162656</v>
+        <v>10.3785003648</v>
       </c>
       <c r="P45">
-        <v>30.0366669344</v>
+        <v>29.8482452352</v>
       </c>
       <c r="Q45">
-        <v>80.13666693440001</v>
+        <v>79.94824523520001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08556007372188154</v>
+        <v>0.08615263325308858</v>
       </c>
       <c r="T45">
-        <v>0.9182465062790195</v>
+        <v>0.9319314839050481</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.707254212095028</v>
+        <v>4.600271161820141</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06629981862172961</v>
+        <v>0.06702112722198675</v>
       </c>
       <c r="C46">
-        <v>266.432666841769</v>
+        <v>247.2391696519249</v>
       </c>
       <c r="D46">
-        <v>429.5806668417691</v>
+        <v>414.9791696519249</v>
       </c>
       <c r="E46">
-        <v>52.548</v>
+        <v>57.13999999999999</v>
       </c>
       <c r="F46">
-        <v>202.048</v>
+        <v>206.64</v>
       </c>
       <c r="G46">
         <v>38.9</v>
@@ -5059,45 +5059,45 @@
         <v>51.4</v>
       </c>
       <c r="M46">
-        <v>11.1732544</v>
+        <v>11.943792</v>
       </c>
       <c r="N46">
-        <v>40.2267456</v>
+        <v>39.456208</v>
       </c>
       <c r="O46">
-        <v>10.3785003648</v>
+        <v>10.179701664</v>
       </c>
       <c r="P46">
-        <v>29.8482452352</v>
+        <v>29.276506336</v>
       </c>
       <c r="Q46">
-        <v>79.94824523520001</v>
+        <v>79.37650633600001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08615263325308858</v>
+        <v>0.08676674040361225</v>
       </c>
       <c r="T46">
-        <v>0.9319314839050481</v>
+        <v>0.9461140970811142</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.600271161820141</v>
+        <v>4.303490884636973</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06702112722198675</v>
+        <v>0.06692623582224387</v>
       </c>
       <c r="C47">
-        <v>247.2391696519249</v>
+        <v>244.5111057834598</v>
       </c>
       <c r="D47">
-        <v>414.9791696519249</v>
+        <v>416.8431057834599</v>
       </c>
       <c r="E47">
-        <v>57.13999999999999</v>
+        <v>61.732</v>
       </c>
       <c r="F47">
-        <v>206.64</v>
+        <v>211.232</v>
       </c>
       <c r="G47">
         <v>38.9</v>
@@ -5141,28 +5141,28 @@
         <v>51.4</v>
       </c>
       <c r="M47">
-        <v>11.943792</v>
+        <v>12.2092096</v>
       </c>
       <c r="N47">
-        <v>39.456208</v>
+        <v>39.1907904</v>
       </c>
       <c r="O47">
-        <v>10.179701664</v>
+        <v>10.1112239232</v>
       </c>
       <c r="P47">
-        <v>29.276506336</v>
+        <v>29.0795664768</v>
       </c>
       <c r="Q47">
-        <v>79.37650633600001</v>
+        <v>79.17956647680001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08676674040361225</v>
+        <v>0.08740359226341457</v>
       </c>
       <c r="T47">
-        <v>0.9461140970811142</v>
+        <v>0.9608219922266642</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.303490884636973</v>
+        <v>4.209936734970951</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06692623582224387</v>
+        <v>0.06683134442250099</v>
       </c>
       <c r="C48">
-        <v>244.5111057834598</v>
+        <v>241.7998617154792</v>
       </c>
       <c r="D48">
-        <v>416.8431057834599</v>
+        <v>418.7238617154792</v>
       </c>
       <c r="E48">
-        <v>61.732</v>
+        <v>66.32400000000001</v>
       </c>
       <c r="F48">
-        <v>211.232</v>
+        <v>215.824</v>
       </c>
       <c r="G48">
         <v>38.9</v>
@@ -5223,28 +5223,28 @@
         <v>51.4</v>
       </c>
       <c r="M48">
-        <v>12.2092096</v>
+        <v>12.4746272</v>
       </c>
       <c r="N48">
-        <v>39.1907904</v>
+        <v>38.9253728</v>
       </c>
       <c r="O48">
-        <v>10.1112239232</v>
+        <v>10.0427461824</v>
       </c>
       <c r="P48">
-        <v>29.0795664768</v>
+        <v>28.8826266176</v>
       </c>
       <c r="Q48">
-        <v>79.17956647680001</v>
+        <v>78.9826266176</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08740359226341457</v>
+        <v>0.08806447626886979</v>
       </c>
       <c r="T48">
-        <v>0.9608219922266642</v>
+        <v>0.9760849022833669</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.209936734970951</v>
+        <v>4.120363612950293</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06683134442250099</v>
+        <v>0.06673645302275812</v>
       </c>
       <c r="C49">
-        <v>241.7998617154792</v>
+        <v>239.1056661478123</v>
       </c>
       <c r="D49">
-        <v>418.7238617154792</v>
+        <v>420.6216661478123</v>
       </c>
       <c r="E49">
-        <v>66.32400000000001</v>
+        <v>70.91600000000003</v>
       </c>
       <c r="F49">
-        <v>215.824</v>
+        <v>220.416</v>
       </c>
       <c r="G49">
         <v>38.9</v>
@@ -5305,28 +5305,28 @@
         <v>51.4</v>
       </c>
       <c r="M49">
-        <v>12.4746272</v>
+        <v>12.7400448</v>
       </c>
       <c r="N49">
-        <v>38.9253728</v>
+        <v>38.6599552</v>
       </c>
       <c r="O49">
-        <v>10.0427461824</v>
+        <v>9.9742684416</v>
       </c>
       <c r="P49">
-        <v>28.8826266176</v>
+        <v>28.6856867584</v>
       </c>
       <c r="Q49">
-        <v>78.9826266176</v>
+        <v>78.7856867584</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08806447626886979</v>
+        <v>0.08875077888991945</v>
       </c>
       <c r="T49">
-        <v>0.9760849022833669</v>
+        <v>0.9919348473422506</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.120363612950293</v>
+        <v>4.034522704347162</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06673645302275812</v>
+        <v>0.06791409162301523</v>
       </c>
       <c r="C50">
-        <v>239.1056661478123</v>
+        <v>212.114359922428</v>
       </c>
       <c r="D50">
-        <v>420.6216661478123</v>
+        <v>398.222359922428</v>
       </c>
       <c r="E50">
-        <v>70.916</v>
+        <v>75.50799999999998</v>
       </c>
       <c r="F50">
-        <v>220.416</v>
+        <v>225.008</v>
       </c>
       <c r="G50">
         <v>38.9</v>
@@ -5387,45 +5387,45 @@
         <v>51.4</v>
       </c>
       <c r="M50">
-        <v>12.7400448</v>
+        <v>13.7929904</v>
       </c>
       <c r="N50">
-        <v>38.6599552</v>
+        <v>37.6070096</v>
       </c>
       <c r="O50">
-        <v>9.9742684416</v>
+        <v>9.7026084768</v>
       </c>
       <c r="P50">
-        <v>28.6856867584</v>
+        <v>27.9044011232</v>
       </c>
       <c r="Q50">
-        <v>78.7856867584</v>
+        <v>78.0044011232</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08875077888991945</v>
+        <v>0.08946399533924557</v>
       </c>
       <c r="T50">
-        <v>0.9919348473422505</v>
+        <v>1.008406358874032</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.034522704347162</v>
+        <v>3.726530542644328</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06791409162301523</v>
+        <v>0.06784517022327237</v>
       </c>
       <c r="C51">
-        <v>212.114359922428</v>
+        <v>208.7673511008488</v>
       </c>
       <c r="D51">
-        <v>398.222359922428</v>
+        <v>399.4673511008488</v>
       </c>
       <c r="E51">
-        <v>75.50799999999998</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F51">
-        <v>225.008</v>
+        <v>229.6</v>
       </c>
       <c r="G51">
         <v>38.9</v>
@@ -5469,28 +5469,28 @@
         <v>51.4</v>
       </c>
       <c r="M51">
-        <v>13.7929904</v>
+        <v>14.07448</v>
       </c>
       <c r="N51">
-        <v>37.6070096</v>
+        <v>37.32552</v>
       </c>
       <c r="O51">
-        <v>9.7026084768</v>
+        <v>9.629984159999999</v>
       </c>
       <c r="P51">
-        <v>27.9044011232</v>
+        <v>27.69553584</v>
       </c>
       <c r="Q51">
-        <v>78.0044011232</v>
+        <v>77.79553584</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08946399533924557</v>
+        <v>0.09020574044654474</v>
       </c>
       <c r="T51">
-        <v>1.008406358874032</v>
+        <v>1.025536730867084</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.726530542644328</v>
+        <v>3.651999931791441</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06784517022327237</v>
+        <v>0.06777624882352949</v>
       </c>
       <c r="C52">
-        <v>208.7673511008488</v>
+        <v>205.4281513039468</v>
       </c>
       <c r="D52">
-        <v>399.4673511008488</v>
+        <v>400.7201513039468</v>
       </c>
       <c r="E52">
-        <v>80.09999999999999</v>
+        <v>84.69200000000001</v>
       </c>
       <c r="F52">
-        <v>229.6</v>
+        <v>234.192</v>
       </c>
       <c r="G52">
         <v>38.9</v>
@@ -5551,28 +5551,28 @@
         <v>51.4</v>
       </c>
       <c r="M52">
-        <v>14.07448</v>
+        <v>14.3559696</v>
       </c>
       <c r="N52">
-        <v>37.32552</v>
+        <v>37.0440304</v>
       </c>
       <c r="O52">
-        <v>9.629984159999999</v>
+        <v>9.557359843199999</v>
       </c>
       <c r="P52">
-        <v>27.69553584</v>
+        <v>27.4866705568</v>
       </c>
       <c r="Q52">
-        <v>77.79553584</v>
+        <v>77.5866705568</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09020574044654474</v>
+        <v>0.09097776086434591</v>
       </c>
       <c r="T52">
-        <v>1.025536730867084</v>
+        <v>1.043366301716995</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.651999931791441</v>
+        <v>3.580392089991609</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06777624882352949</v>
+        <v>0.06770732742378663</v>
       </c>
       <c r="C53">
-        <v>205.4281513039468</v>
+        <v>202.0968342343097</v>
       </c>
       <c r="D53">
-        <v>400.7201513039468</v>
+        <v>401.9808342343097</v>
       </c>
       <c r="E53">
-        <v>84.69200000000001</v>
+        <v>89.28399999999999</v>
       </c>
       <c r="F53">
-        <v>234.192</v>
+        <v>238.784</v>
       </c>
       <c r="G53">
         <v>38.9</v>
@@ -5633,28 +5633,28 @@
         <v>51.4</v>
       </c>
       <c r="M53">
-        <v>14.3559696</v>
+        <v>14.6374592</v>
       </c>
       <c r="N53">
-        <v>37.0440304</v>
+        <v>36.7625408</v>
       </c>
       <c r="O53">
-        <v>9.557359843199999</v>
+        <v>9.4847355264</v>
       </c>
       <c r="P53">
-        <v>27.4866705568</v>
+        <v>27.27780527359999</v>
       </c>
       <c r="Q53">
-        <v>77.5866705568</v>
+        <v>77.37780527359999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09097776086434591</v>
+        <v>0.09178194879955547</v>
       </c>
       <c r="T53">
-        <v>1.043366301716995</v>
+        <v>1.06193877135232</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.580392089991609</v>
+        <v>3.511538395953308</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06770732742378663</v>
+        <v>0.06873953402404376</v>
       </c>
       <c r="C54">
-        <v>202.0968342343097</v>
+        <v>179.4169659350399</v>
       </c>
       <c r="D54">
-        <v>401.9808342343097</v>
+        <v>383.89296593504</v>
       </c>
       <c r="E54">
-        <v>89.28399999999999</v>
+        <v>93.876</v>
       </c>
       <c r="F54">
-        <v>238.784</v>
+        <v>243.376</v>
       </c>
       <c r="G54">
         <v>38.9</v>
@@ -5715,45 +5715,45 @@
         <v>51.4</v>
       </c>
       <c r="M54">
-        <v>14.6374592</v>
+        <v>15.6004016</v>
       </c>
       <c r="N54">
-        <v>36.7625408</v>
+        <v>35.79959839999999</v>
       </c>
       <c r="O54">
-        <v>9.4847355264</v>
+        <v>9.236296387199999</v>
       </c>
       <c r="P54">
-        <v>27.27780527359999</v>
+        <v>26.56330201279999</v>
       </c>
       <c r="Q54">
-        <v>77.37780527359999</v>
+        <v>76.66330201279999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09178194879955547</v>
+        <v>0.09262035749796543</v>
       </c>
       <c r="T54">
-        <v>1.06193877135232</v>
+        <v>1.081301558844467</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.511538395953308</v>
+        <v>3.294786975227611</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06873953402404376</v>
+        <v>0.06869138862430087</v>
       </c>
       <c r="C55">
-        <v>179.4169659350399</v>
+        <v>175.6323734980659</v>
       </c>
       <c r="D55">
-        <v>383.89296593504</v>
+        <v>384.7003734980659</v>
       </c>
       <c r="E55">
-        <v>93.876</v>
+        <v>98.46800000000002</v>
       </c>
       <c r="F55">
-        <v>243.376</v>
+        <v>247.968</v>
       </c>
       <c r="G55">
         <v>38.9</v>
@@ -5797,28 +5797,28 @@
         <v>51.4</v>
       </c>
       <c r="M55">
-        <v>15.6004016</v>
+        <v>15.8947488</v>
       </c>
       <c r="N55">
-        <v>35.79959839999999</v>
+        <v>35.5052512</v>
       </c>
       <c r="O55">
-        <v>9.236296387199999</v>
+        <v>9.160354809599999</v>
       </c>
       <c r="P55">
-        <v>26.56330201279999</v>
+        <v>26.3448963904</v>
       </c>
       <c r="Q55">
-        <v>76.66330201279999</v>
+        <v>76.4448963904</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09262035749796543</v>
+        <v>0.09349521874848016</v>
       </c>
       <c r="T55">
-        <v>1.081301558844467</v>
+        <v>1.101506206662359</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.294786975227611</v>
+        <v>3.233772401612285</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06869138862430087</v>
+        <v>0.068643243224558</v>
       </c>
       <c r="C56">
-        <v>175.6323734980659</v>
+        <v>171.8511845147512</v>
       </c>
       <c r="D56">
-        <v>384.7003734980659</v>
+        <v>385.5111845147512</v>
       </c>
       <c r="E56">
-        <v>98.46800000000002</v>
+        <v>103.06</v>
       </c>
       <c r="F56">
-        <v>247.968</v>
+        <v>252.56</v>
       </c>
       <c r="G56">
         <v>38.9</v>
@@ -5879,28 +5879,28 @@
         <v>51.4</v>
       </c>
       <c r="M56">
-        <v>15.8947488</v>
+        <v>16.189096</v>
       </c>
       <c r="N56">
-        <v>35.5052512</v>
+        <v>35.210904</v>
       </c>
       <c r="O56">
-        <v>9.160354809599999</v>
+        <v>9.084413231999999</v>
       </c>
       <c r="P56">
-        <v>26.3448963904</v>
+        <v>26.126490768</v>
       </c>
       <c r="Q56">
-        <v>76.4448963904</v>
+        <v>76.22649076800001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09349521874848016</v>
+        <v>0.09440896272124001</v>
       </c>
       <c r="T56">
-        <v>1.101506206662359</v>
+        <v>1.122608838827714</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.233772401612285</v>
+        <v>3.174976539764789</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.068643243224558</v>
+        <v>0.06859509782481513</v>
       </c>
       <c r="C57">
-        <v>171.8511845147512</v>
+        <v>168.0734205503433</v>
       </c>
       <c r="D57">
-        <v>385.5111845147512</v>
+        <v>386.3254205503434</v>
       </c>
       <c r="E57">
-        <v>103.06</v>
+        <v>107.652</v>
       </c>
       <c r="F57">
-        <v>252.56</v>
+        <v>257.152</v>
       </c>
       <c r="G57">
         <v>38.9</v>
@@ -5961,28 +5961,28 @@
         <v>51.4</v>
       </c>
       <c r="M57">
-        <v>16.189096</v>
+        <v>16.4834432</v>
       </c>
       <c r="N57">
-        <v>35.210904</v>
+        <v>34.9165568</v>
       </c>
       <c r="O57">
-        <v>9.084413231999999</v>
+        <v>9.008471654399999</v>
       </c>
       <c r="P57">
-        <v>26.126490768</v>
+        <v>25.9080851456</v>
       </c>
       <c r="Q57">
-        <v>76.22649076800001</v>
+        <v>76.00808514560001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09440896272124001</v>
+        <v>0.09536424051094347</v>
       </c>
       <c r="T57">
-        <v>1.122608838827714</v>
+        <v>1.144670681546039</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.174976539764789</v>
+        <v>3.118280530126132</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06859509782481513</v>
+        <v>0.06854695242507226</v>
       </c>
       <c r="C58">
-        <v>168.0734205503433</v>
+        <v>164.2991033526657</v>
       </c>
       <c r="D58">
-        <v>386.3254205503434</v>
+        <v>387.1431033526657</v>
       </c>
       <c r="E58">
-        <v>107.652</v>
+        <v>112.244</v>
       </c>
       <c r="F58">
-        <v>257.152</v>
+        <v>261.744</v>
       </c>
       <c r="G58">
         <v>38.9</v>
@@ -6043,28 +6043,28 @@
         <v>51.4</v>
       </c>
       <c r="M58">
-        <v>16.4834432</v>
+        <v>16.7777904</v>
       </c>
       <c r="N58">
-        <v>34.9165568</v>
+        <v>34.62220959999999</v>
       </c>
       <c r="O58">
-        <v>9.008471654399999</v>
+        <v>8.932530076799997</v>
       </c>
       <c r="P58">
-        <v>25.9080851456</v>
+        <v>25.68967952319999</v>
       </c>
       <c r="Q58">
-        <v>76.00808514560001</v>
+        <v>75.78967952319999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09536424051094347</v>
+        <v>0.09636394982574945</v>
       </c>
       <c r="T58">
-        <v>1.144670681546039</v>
+        <v>1.167758656483821</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.118280530126132</v>
+        <v>3.063573854159007</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06854695242507226</v>
+        <v>0.06849880702532939</v>
       </c>
       <c r="C59">
-        <v>164.2991033526657</v>
+        <v>160.5282548540557</v>
       </c>
       <c r="D59">
-        <v>387.1431033526657</v>
+        <v>387.9642548540558</v>
       </c>
       <c r="E59">
-        <v>112.244</v>
+        <v>116.836</v>
       </c>
       <c r="F59">
-        <v>261.744</v>
+        <v>266.336</v>
       </c>
       <c r="G59">
         <v>38.9</v>
@@ -6125,28 +6125,28 @@
         <v>51.4</v>
       </c>
       <c r="M59">
-        <v>16.7777904</v>
+        <v>17.0721376</v>
       </c>
       <c r="N59">
-        <v>34.62220959999999</v>
+        <v>34.3278624</v>
       </c>
       <c r="O59">
-        <v>8.932530076799997</v>
+        <v>8.856588499200001</v>
       </c>
       <c r="P59">
-        <v>25.68967952319999</v>
+        <v>25.4712739008</v>
       </c>
       <c r="Q59">
-        <v>75.78967952319999</v>
+        <v>75.57127390080001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09636394982574945</v>
+        <v>0.09741126434602235</v>
       </c>
       <c r="T59">
-        <v>1.167758656483821</v>
+        <v>1.191946058799592</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.063573854159007</v>
+        <v>3.010753615294197</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0684988070253294</v>
+        <v>0.07186534562558651</v>
       </c>
       <c r="C60">
-        <v>160.5282548540555</v>
+        <v>105.8277061991678</v>
       </c>
       <c r="D60">
-        <v>387.9642548540555</v>
+        <v>337.8557061991679</v>
       </c>
       <c r="E60">
-        <v>116.836</v>
+        <v>121.428</v>
       </c>
       <c r="F60">
-        <v>266.336</v>
+        <v>270.928</v>
       </c>
       <c r="G60">
         <v>38.9</v>
@@ -6207,45 +6207,45 @@
         <v>51.4</v>
       </c>
       <c r="M60">
-        <v>17.0721376</v>
+        <v>19.4797232</v>
       </c>
       <c r="N60">
-        <v>34.3278624</v>
+        <v>31.9202768</v>
       </c>
       <c r="O60">
-        <v>8.856588499200001</v>
+        <v>8.235431414399999</v>
       </c>
       <c r="P60">
-        <v>25.4712739008</v>
+        <v>23.6848453856</v>
       </c>
       <c r="Q60">
-        <v>75.57127390080001</v>
+        <v>73.78484538559999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09741126434602235</v>
+        <v>0.09850966737947929</v>
       </c>
       <c r="T60">
-        <v>1.191946058799592</v>
+        <v>1.21731333439906</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.010753615294198</v>
+        <v>2.638641189726966</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07186534562558651</v>
+        <v>0.07187507622584363</v>
       </c>
       <c r="C61">
-        <v>105.8277061991678</v>
+        <v>101.1096264595292</v>
       </c>
       <c r="D61">
-        <v>337.8557061991679</v>
+        <v>337.7296264595292</v>
       </c>
       <c r="E61">
-        <v>121.428</v>
+        <v>126.02</v>
       </c>
       <c r="F61">
-        <v>270.928</v>
+        <v>275.52</v>
       </c>
       <c r="G61">
         <v>38.9</v>
@@ -6289,28 +6289,28 @@
         <v>51.4</v>
       </c>
       <c r="M61">
-        <v>19.4797232</v>
+        <v>19.809888</v>
       </c>
       <c r="N61">
-        <v>31.9202768</v>
+        <v>31.590112</v>
       </c>
       <c r="O61">
-        <v>8.235431414399999</v>
+        <v>8.150248895999999</v>
       </c>
       <c r="P61">
-        <v>23.6848453856</v>
+        <v>23.439863104</v>
       </c>
       <c r="Q61">
-        <v>73.78484538559999</v>
+        <v>73.53986310400001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09850966737947929</v>
+        <v>0.09966299056460909</v>
       </c>
       <c r="T61">
-        <v>1.21731333439906</v>
+        <v>1.243948973778501</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.638641189726966</v>
+        <v>2.594663836564851</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07187507622584363</v>
+        <v>0.07188480682610077</v>
       </c>
       <c r="C62">
-        <v>101.1096264595292</v>
+        <v>96.39164078472714</v>
       </c>
       <c r="D62">
-        <v>337.7296264595292</v>
+        <v>337.6036407847271</v>
       </c>
       <c r="E62">
-        <v>126.02</v>
+        <v>130.612</v>
       </c>
       <c r="F62">
-        <v>275.52</v>
+        <v>280.112</v>
       </c>
       <c r="G62">
         <v>38.9</v>
@@ -6371,28 +6371,28 @@
         <v>51.4</v>
       </c>
       <c r="M62">
-        <v>19.809888</v>
+        <v>20.1400528</v>
       </c>
       <c r="N62">
-        <v>31.590112</v>
+        <v>31.2599472</v>
       </c>
       <c r="O62">
-        <v>8.150248895999999</v>
+        <v>8.065066377600001</v>
       </c>
       <c r="P62">
-        <v>23.439863104</v>
+        <v>23.1948808224</v>
       </c>
       <c r="Q62">
-        <v>73.53986310400001</v>
+        <v>73.2948808224</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09966299056460909</v>
+        <v>0.1008754585284635</v>
       </c>
       <c r="T62">
-        <v>1.243948973778501</v>
+        <v>1.271950543382528</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.594663836564851</v>
+        <v>2.55212836383428</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07188480682610077</v>
+        <v>0.07189453742635789</v>
       </c>
       <c r="C63">
-        <v>96.39164078472714</v>
+        <v>91.67374906953205</v>
       </c>
       <c r="D63">
-        <v>337.6036407847271</v>
+        <v>337.4777490695321</v>
       </c>
       <c r="E63">
-        <v>130.612</v>
+        <v>135.204</v>
       </c>
       <c r="F63">
-        <v>280.112</v>
+        <v>284.704</v>
       </c>
       <c r="G63">
         <v>38.9</v>
@@ -6453,28 +6453,28 @@
         <v>51.4</v>
       </c>
       <c r="M63">
-        <v>20.1400528</v>
+        <v>20.4702176</v>
       </c>
       <c r="N63">
-        <v>31.2599472</v>
+        <v>30.9297824</v>
       </c>
       <c r="O63">
-        <v>8.065066377600001</v>
+        <v>7.979883859199999</v>
       </c>
       <c r="P63">
-        <v>23.1948808224</v>
+        <v>22.9498985408</v>
       </c>
       <c r="Q63">
-        <v>73.2948808224</v>
+        <v>73.0498985408</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1008754585284635</v>
+        <v>0.1021517405956787</v>
       </c>
       <c r="T63">
-        <v>1.271950543382528</v>
+        <v>1.301425879807821</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.55212836383428</v>
+        <v>2.510965003127275</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07189453742635789</v>
+        <v>0.07372736202661501</v>
       </c>
       <c r="C64">
-        <v>91.67374906953205</v>
+        <v>64.93366648498409</v>
       </c>
       <c r="D64">
-        <v>337.4777490695321</v>
+        <v>315.3296664849841</v>
       </c>
       <c r="E64">
-        <v>135.204</v>
+        <v>139.796</v>
       </c>
       <c r="F64">
-        <v>284.704</v>
+        <v>289.296</v>
       </c>
       <c r="G64">
         <v>38.9</v>
@@ -6535,45 +6535,45 @@
         <v>51.4</v>
       </c>
       <c r="M64">
-        <v>20.4702176</v>
+        <v>21.9286368</v>
       </c>
       <c r="N64">
-        <v>30.9297824</v>
+        <v>29.4713632</v>
       </c>
       <c r="O64">
-        <v>7.979883859199999</v>
+        <v>7.6036117056</v>
       </c>
       <c r="P64">
-        <v>22.9498985408</v>
+        <v>21.8677514944</v>
       </c>
       <c r="Q64">
-        <v>73.0498985408</v>
+        <v>71.96775149440001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1021517405956787</v>
+        <v>0.1034970108827433</v>
       </c>
       <c r="T64">
-        <v>1.301425879807821</v>
+        <v>1.332494477661508</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.510965003127275</v>
+        <v>2.343966953750631</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07372736202661501</v>
+        <v>0.07376603062687215</v>
       </c>
       <c r="C65">
-        <v>64.93366648498409</v>
+        <v>59.90566049667598</v>
       </c>
       <c r="D65">
-        <v>315.3296664849841</v>
+        <v>314.893660496676</v>
       </c>
       <c r="E65">
-        <v>139.796</v>
+        <v>144.388</v>
       </c>
       <c r="F65">
-        <v>289.296</v>
+        <v>293.888</v>
       </c>
       <c r="G65">
         <v>38.9</v>
@@ -6617,28 +6617,28 @@
         <v>51.4</v>
       </c>
       <c r="M65">
-        <v>21.9286368</v>
+        <v>22.2767104</v>
       </c>
       <c r="N65">
-        <v>29.4713632</v>
+        <v>29.1232896</v>
       </c>
       <c r="O65">
-        <v>7.6036117056</v>
+        <v>7.5138087168</v>
       </c>
       <c r="P65">
-        <v>21.8677514944</v>
+        <v>21.6094808832</v>
       </c>
       <c r="Q65">
-        <v>71.96775149440001</v>
+        <v>71.7094808832</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1034970108827433</v>
+        <v>0.1049170184079782</v>
       </c>
       <c r="T65">
-        <v>1.332494477661508</v>
+        <v>1.365289108729288</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.343966953750631</v>
+        <v>2.307342470098278</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07376603062687215</v>
+        <v>0.07380469922712926</v>
       </c>
       <c r="C66">
-        <v>59.90566049667598</v>
+        <v>54.8788585735241</v>
       </c>
       <c r="D66">
-        <v>314.893660496676</v>
+        <v>314.4588585735241</v>
       </c>
       <c r="E66">
-        <v>144.388</v>
+        <v>148.98</v>
       </c>
       <c r="F66">
-        <v>293.888</v>
+        <v>298.48</v>
       </c>
       <c r="G66">
         <v>38.9</v>
@@ -6699,28 +6699,28 @@
         <v>51.4</v>
       </c>
       <c r="M66">
-        <v>22.2767104</v>
+        <v>22.624784</v>
       </c>
       <c r="N66">
-        <v>29.1232896</v>
+        <v>28.775216</v>
       </c>
       <c r="O66">
-        <v>7.5138087168</v>
+        <v>7.424005727999999</v>
       </c>
       <c r="P66">
-        <v>21.6094808832</v>
+        <v>21.351210272</v>
       </c>
       <c r="Q66">
-        <v>71.7094808832</v>
+        <v>71.451210272</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1049170184079782</v>
+        <v>0.1064181692203693</v>
       </c>
       <c r="T66">
-        <v>1.365289108729288</v>
+        <v>1.399957718715227</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.307342470098278</v>
+        <v>2.271844893635227</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07380469922712926</v>
+        <v>0.0738433678273864</v>
       </c>
       <c r="C67">
-        <v>54.8788585735241</v>
+        <v>49.85325573472306</v>
       </c>
       <c r="D67">
-        <v>314.4588585735241</v>
+        <v>314.0252557347231</v>
       </c>
       <c r="E67">
-        <v>148.98</v>
+        <v>153.572</v>
       </c>
       <c r="F67">
-        <v>298.48</v>
+        <v>303.072</v>
       </c>
       <c r="G67">
         <v>38.9</v>
@@ -6781,28 +6781,28 @@
         <v>51.4</v>
       </c>
       <c r="M67">
-        <v>22.624784</v>
+        <v>22.9728576</v>
       </c>
       <c r="N67">
-        <v>28.775216</v>
+        <v>28.4271424</v>
       </c>
       <c r="O67">
-        <v>7.424005727999999</v>
+        <v>7.334202739199999</v>
       </c>
       <c r="P67">
-        <v>21.351210272</v>
+        <v>21.0929396608</v>
       </c>
       <c r="Q67">
-        <v>71.451210272</v>
+        <v>71.19293966079999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1064181692203693</v>
+        <v>0.1080076230217247</v>
       </c>
       <c r="T67">
-        <v>1.399957718715227</v>
+        <v>1.436665658700339</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.271844893635227</v>
+        <v>2.237423001307421</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0738433678273864</v>
+        <v>0.07388203642764352</v>
       </c>
       <c r="C68">
-        <v>49.85325573472306</v>
+        <v>44.82884702690262</v>
       </c>
       <c r="D68">
-        <v>314.0252557347231</v>
+        <v>313.5928470269026</v>
       </c>
       <c r="E68">
-        <v>153.572</v>
+        <v>158.164</v>
       </c>
       <c r="F68">
-        <v>303.072</v>
+        <v>307.664</v>
       </c>
       <c r="G68">
         <v>38.9</v>
@@ -6863,28 +6863,28 @@
         <v>51.4</v>
       </c>
       <c r="M68">
-        <v>22.9728576</v>
+        <v>23.3209312</v>
       </c>
       <c r="N68">
-        <v>28.4271424</v>
+        <v>28.0790688</v>
       </c>
       <c r="O68">
-        <v>7.334202739199999</v>
+        <v>7.2443997504</v>
       </c>
       <c r="P68">
-        <v>21.0929396608</v>
+        <v>20.8346690496</v>
       </c>
       <c r="Q68">
-        <v>71.19293966079999</v>
+        <v>70.9346690496</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1080076230217247</v>
+        <v>0.1096934073564955</v>
       </c>
       <c r="T68">
-        <v>1.436665658700339</v>
+        <v>1.475598322320913</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.237423001307421</v>
+        <v>2.204028628153579</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07388203642764352</v>
+        <v>0.07392070502790066</v>
       </c>
       <c r="C69">
-        <v>44.82884702690262</v>
+        <v>39.80562752393672</v>
       </c>
       <c r="D69">
-        <v>313.5928470269026</v>
+        <v>313.1616275239368</v>
       </c>
       <c r="E69">
-        <v>158.164</v>
+        <v>162.756</v>
       </c>
       <c r="F69">
-        <v>307.664</v>
+        <v>312.256</v>
       </c>
       <c r="G69">
         <v>38.9</v>
@@ -6945,28 +6945,28 @@
         <v>51.4</v>
       </c>
       <c r="M69">
-        <v>23.3209312</v>
+        <v>23.6690048</v>
       </c>
       <c r="N69">
-        <v>28.0790688</v>
+        <v>27.7309952</v>
       </c>
       <c r="O69">
-        <v>7.2443997504</v>
+        <v>7.154596761599999</v>
       </c>
       <c r="P69">
-        <v>20.8346690496</v>
+        <v>20.5763984384</v>
       </c>
       <c r="Q69">
-        <v>70.9346690496</v>
+        <v>70.6763984384</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1096934073564955</v>
+        <v>0.1114845532121895</v>
       </c>
       <c r="T69">
-        <v>1.475598322320913</v>
+        <v>1.516964277417772</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.204028628153579</v>
+        <v>2.171616442445438</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07392070502790066</v>
+        <v>0.07395937362815778</v>
       </c>
       <c r="C70">
-        <v>39.80562752393672</v>
+        <v>34.78359232675871</v>
       </c>
       <c r="D70">
-        <v>313.1616275239368</v>
+        <v>312.7315923267587</v>
       </c>
       <c r="E70">
-        <v>162.756</v>
+        <v>167.348</v>
       </c>
       <c r="F70">
-        <v>312.256</v>
+        <v>316.848</v>
       </c>
       <c r="G70">
         <v>38.9</v>
@@ -7027,28 +7027,28 @@
         <v>51.4</v>
       </c>
       <c r="M70">
-        <v>23.6690048</v>
+        <v>24.0170784</v>
       </c>
       <c r="N70">
-        <v>27.7309952</v>
+        <v>27.3829216</v>
       </c>
       <c r="O70">
-        <v>7.154596761599999</v>
+        <v>7.064793772799999</v>
       </c>
       <c r="P70">
-        <v>20.5763984384</v>
+        <v>20.3181278272</v>
       </c>
       <c r="Q70">
-        <v>70.6763984384</v>
+        <v>70.4181278272</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1114845532121895</v>
+        <v>0.1133912568650251</v>
       </c>
       <c r="T70">
-        <v>1.516964277417772</v>
+        <v>1.560999003811203</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.171616442445438</v>
+        <v>2.140143740381011</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07395937362815778</v>
+        <v>0.07399804222841491</v>
       </c>
       <c r="C71">
-        <v>34.78359232675871</v>
+        <v>29.76273656317403</v>
       </c>
       <c r="D71">
-        <v>312.7315923267587</v>
+        <v>312.3027365631741</v>
       </c>
       <c r="E71">
-        <v>167.348</v>
+        <v>171.94</v>
       </c>
       <c r="F71">
-        <v>316.848</v>
+        <v>321.44</v>
       </c>
       <c r="G71">
         <v>38.9</v>
@@ -7109,28 +7109,28 @@
         <v>51.4</v>
       </c>
       <c r="M71">
-        <v>24.0170784</v>
+        <v>24.365152</v>
       </c>
       <c r="N71">
-        <v>27.3829216</v>
+        <v>27.034848</v>
       </c>
       <c r="O71">
-        <v>7.064793772799999</v>
+        <v>6.974990783999999</v>
       </c>
       <c r="P71">
-        <v>20.3181278272</v>
+        <v>20.059857216</v>
       </c>
       <c r="Q71">
-        <v>70.4181278272</v>
+        <v>70.15985721600001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1133912568650251</v>
+        <v>0.1154250740947164</v>
       </c>
       <c r="T71">
-        <v>1.560999003811203</v>
+        <v>1.607969378630862</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.140143740381011</v>
+        <v>2.109570258375568</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07399804222841491</v>
+        <v>0.07403671082867203</v>
       </c>
       <c r="C72">
-        <v>29.76273656317403</v>
+        <v>24.74305538767743</v>
       </c>
       <c r="D72">
-        <v>312.3027365631741</v>
+        <v>311.8750553876775</v>
       </c>
       <c r="E72">
-        <v>171.94</v>
+        <v>176.532</v>
       </c>
       <c r="F72">
-        <v>321.44</v>
+        <v>326.032</v>
       </c>
       <c r="G72">
         <v>38.9</v>
@@ -7191,28 +7191,28 @@
         <v>51.4</v>
       </c>
       <c r="M72">
-        <v>24.365152</v>
+        <v>24.7132256</v>
       </c>
       <c r="N72">
-        <v>27.034848</v>
+        <v>26.68677439999999</v>
       </c>
       <c r="O72">
-        <v>6.974990783999999</v>
+        <v>6.885187795199998</v>
       </c>
       <c r="P72">
-        <v>20.059857216</v>
+        <v>19.80158660479999</v>
       </c>
       <c r="Q72">
-        <v>70.15985721600001</v>
+        <v>69.9015866048</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1154250740947164</v>
+        <v>0.1175991545816277</v>
       </c>
       <c r="T72">
-        <v>1.607969378630862</v>
+        <v>1.658179089644982</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.109570258375568</v>
+        <v>2.079858001215348</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07403671082867204</v>
+        <v>0.07407537942892917</v>
       </c>
       <c r="C73">
-        <v>24.74305538767732</v>
+        <v>19.72454398126928</v>
       </c>
       <c r="D73">
-        <v>311.8750553876773</v>
+        <v>311.4485439812693</v>
       </c>
       <c r="E73">
-        <v>176.532</v>
+        <v>181.124</v>
       </c>
       <c r="F73">
-        <v>326.032</v>
+        <v>330.624</v>
       </c>
       <c r="G73">
         <v>38.9</v>
@@ -7273,28 +7273,28 @@
         <v>51.4</v>
       </c>
       <c r="M73">
-        <v>24.7132256</v>
+        <v>25.0612992</v>
       </c>
       <c r="N73">
-        <v>26.6867744</v>
+        <v>26.3387008</v>
       </c>
       <c r="O73">
-        <v>6.885187795199999</v>
+        <v>6.7953848064</v>
       </c>
       <c r="P73">
-        <v>19.8015866048</v>
+        <v>19.5433159936</v>
       </c>
       <c r="Q73">
-        <v>69.9015866048</v>
+        <v>69.6433159936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1175991545816277</v>
+        <v>0.1199285265318898</v>
       </c>
       <c r="T73">
-        <v>1.658179089644981</v>
+        <v>1.711975208588679</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.079858001215349</v>
+        <v>2.050971084531803</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07407537942892917</v>
+        <v>0.07411404802918628</v>
       </c>
       <c r="C74">
-        <v>19.72454398126928</v>
+        <v>14.70719755127595</v>
       </c>
       <c r="D74">
-        <v>311.4485439812693</v>
+        <v>311.023197551276</v>
       </c>
       <c r="E74">
-        <v>181.124</v>
+        <v>185.716</v>
       </c>
       <c r="F74">
-        <v>330.624</v>
+        <v>335.216</v>
       </c>
       <c r="G74">
         <v>38.9</v>
@@ -7355,28 +7355,28 @@
         <v>51.4</v>
       </c>
       <c r="M74">
-        <v>25.0612992</v>
+        <v>25.4093728</v>
       </c>
       <c r="N74">
-        <v>26.3387008</v>
+        <v>25.9906272</v>
       </c>
       <c r="O74">
-        <v>6.7953848064</v>
+        <v>6.705581817599999</v>
       </c>
       <c r="P74">
-        <v>19.5433159936</v>
+        <v>19.2850453824</v>
       </c>
       <c r="Q74">
-        <v>69.6433159936</v>
+        <v>69.38504538239999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1199285265318898</v>
+        <v>0.1224304445525418</v>
       </c>
       <c r="T74">
-        <v>1.711975208588679</v>
+        <v>1.769756225231912</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.050971084531803</v>
+        <v>2.022875590223148</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07411404802918628</v>
+        <v>0.0819496526294434</v>
       </c>
       <c r="C75">
-        <v>14.70719755127595</v>
+        <v>-57.3005207268717</v>
       </c>
       <c r="D75">
-        <v>311.023197551276</v>
+        <v>243.6074792731283</v>
       </c>
       <c r="E75">
-        <v>185.716</v>
+        <v>190.308</v>
       </c>
       <c r="F75">
-        <v>335.216</v>
+        <v>339.808</v>
       </c>
       <c r="G75">
         <v>38.9</v>
@@ -7437,45 +7437,45 @@
         <v>51.4</v>
       </c>
       <c r="M75">
-        <v>25.4093728</v>
+        <v>30.58272</v>
       </c>
       <c r="N75">
-        <v>25.9906272</v>
+        <v>20.81728</v>
       </c>
       <c r="O75">
-        <v>6.705581817599999</v>
+        <v>5.37085824</v>
       </c>
       <c r="P75">
-        <v>19.2850453824</v>
+        <v>15.44642176</v>
       </c>
       <c r="Q75">
-        <v>69.38504538239999</v>
+        <v>65.54642176</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1224304445525418</v>
+        <v>0.1251248178055516</v>
       </c>
       <c r="T75">
-        <v>1.769756225231912</v>
+        <v>1.831981935463084</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.022875590223148</v>
+        <v>1.680687656297412</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0819496526294434</v>
+        <v>0.08209368522970052</v>
       </c>
       <c r="C76">
-        <v>-57.3005207268717</v>
+        <v>-62.85928446165713</v>
       </c>
       <c r="D76">
-        <v>243.6074792731283</v>
+        <v>242.6407155383429</v>
       </c>
       <c r="E76">
-        <v>190.308</v>
+        <v>194.9</v>
       </c>
       <c r="F76">
-        <v>339.808</v>
+        <v>344.4</v>
       </c>
       <c r="G76">
         <v>38.9</v>
@@ -7519,28 +7519,28 @@
         <v>51.4</v>
       </c>
       <c r="M76">
-        <v>30.58272</v>
+        <v>30.996</v>
       </c>
       <c r="N76">
-        <v>20.81728</v>
+        <v>20.404</v>
       </c>
       <c r="O76">
-        <v>5.37085824</v>
+        <v>5.264232000000001</v>
       </c>
       <c r="P76">
-        <v>15.44642176</v>
+        <v>15.139768</v>
       </c>
       <c r="Q76">
-        <v>65.54642176</v>
+        <v>65.239768</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1251248178055516</v>
+        <v>0.1280347409188021</v>
       </c>
       <c r="T76">
-        <v>1.831981935463084</v>
+        <v>1.899185702512751</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.680687656297412</v>
+        <v>1.65827848754678</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08209368522970052</v>
+        <v>0.08223771782995765</v>
       </c>
       <c r="C77">
-        <v>-62.85928446165713</v>
+        <v>-68.41040526473068</v>
       </c>
       <c r="D77">
-        <v>242.6407155383429</v>
+        <v>241.6815947352693</v>
       </c>
       <c r="E77">
-        <v>194.9</v>
+        <v>199.492</v>
       </c>
       <c r="F77">
-        <v>344.4</v>
+        <v>348.992</v>
       </c>
       <c r="G77">
         <v>38.9</v>
@@ -7601,28 +7601,28 @@
         <v>51.4</v>
       </c>
       <c r="M77">
-        <v>30.996</v>
+        <v>31.40928</v>
       </c>
       <c r="N77">
-        <v>20.404</v>
+        <v>19.99072</v>
       </c>
       <c r="O77">
-        <v>5.264232000000001</v>
+        <v>5.15760576</v>
       </c>
       <c r="P77">
-        <v>15.139768</v>
+        <v>14.83311424</v>
       </c>
       <c r="Q77">
-        <v>65.239768</v>
+        <v>64.93311424000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1280347409188021</v>
+        <v>0.1311871576248236</v>
       </c>
       <c r="T77">
-        <v>1.899185702512751</v>
+        <v>1.971989783483224</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.65827848754678</v>
+        <v>1.63645903376327</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08223771782995765</v>
+        <v>0.08238175043021478</v>
       </c>
       <c r="C78">
-        <v>-68.41040526473068</v>
+        <v>-73.95397341318272</v>
       </c>
       <c r="D78">
-        <v>241.6815947352693</v>
+        <v>240.7300265868173</v>
       </c>
       <c r="E78">
-        <v>199.492</v>
+        <v>204.084</v>
       </c>
       <c r="F78">
-        <v>348.992</v>
+        <v>353.584</v>
       </c>
       <c r="G78">
         <v>38.9</v>
@@ -7683,28 +7683,28 @@
         <v>51.4</v>
       </c>
       <c r="M78">
-        <v>31.40928</v>
+        <v>31.82256</v>
       </c>
       <c r="N78">
-        <v>19.99072</v>
+        <v>19.57744</v>
       </c>
       <c r="O78">
-        <v>5.15760576</v>
+        <v>5.05097952</v>
       </c>
       <c r="P78">
-        <v>14.83311424</v>
+        <v>14.52646048</v>
       </c>
       <c r="Q78">
-        <v>64.93311424000001</v>
+        <v>64.62646048000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1311871576248236</v>
+        <v>0.134613697522673</v>
       </c>
       <c r="T78">
-        <v>1.971989783483224</v>
+        <v>2.051124654103302</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.63645903376327</v>
+        <v>1.615206319039072</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08238175043021478</v>
+        <v>0.08252578303047191</v>
       </c>
       <c r="C79">
-        <v>-73.95397341318272</v>
+        <v>-79.49007776789443</v>
       </c>
       <c r="D79">
-        <v>240.7300265868173</v>
+        <v>239.7859222321056</v>
       </c>
       <c r="E79">
-        <v>204.084</v>
+        <v>208.676</v>
       </c>
       <c r="F79">
-        <v>353.584</v>
+        <v>358.176</v>
       </c>
       <c r="G79">
         <v>38.9</v>
@@ -7765,28 +7765,28 @@
         <v>51.4</v>
       </c>
       <c r="M79">
-        <v>31.82256</v>
+        <v>32.23584</v>
       </c>
       <c r="N79">
-        <v>19.57744</v>
+        <v>19.16416</v>
       </c>
       <c r="O79">
-        <v>5.05097952</v>
+        <v>4.944353280000001</v>
       </c>
       <c r="P79">
-        <v>14.52646048</v>
+        <v>14.21980672</v>
       </c>
       <c r="Q79">
-        <v>64.62646048000001</v>
+        <v>64.31980672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.134613697522673</v>
+        <v>0.1383517410475996</v>
       </c>
       <c r="T79">
-        <v>2.051124654103302</v>
+        <v>2.137453603870661</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.615206319039072</v>
+        <v>1.594498545718058</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08252578303047191</v>
+        <v>0.08266981563072903</v>
       </c>
       <c r="C80">
-        <v>-79.49007776789443</v>
+        <v>-85.01880580120081</v>
       </c>
       <c r="D80">
-        <v>239.7859222321056</v>
+        <v>238.8491941987992</v>
       </c>
       <c r="E80">
-        <v>208.676</v>
+        <v>213.268</v>
       </c>
       <c r="F80">
-        <v>358.176</v>
+        <v>362.768</v>
       </c>
       <c r="G80">
         <v>38.9</v>
@@ -7847,28 +7847,28 @@
         <v>51.4</v>
       </c>
       <c r="M80">
-        <v>32.23584</v>
+        <v>32.64912</v>
       </c>
       <c r="N80">
-        <v>19.16416</v>
+        <v>18.75088</v>
       </c>
       <c r="O80">
-        <v>4.944353280000001</v>
+        <v>4.837727039999999</v>
       </c>
       <c r="P80">
-        <v>14.21980672</v>
+        <v>13.91315296</v>
       </c>
       <c r="Q80">
-        <v>64.31980672</v>
+        <v>64.01315296</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1383517410475996</v>
+        <v>0.1424457887177573</v>
       </c>
       <c r="T80">
-        <v>2.137453603870661</v>
+        <v>2.232004358377768</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.594498545718058</v>
+        <v>1.574315019822893</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08266981563072903</v>
+        <v>0.08281384823098617</v>
       </c>
       <c r="C81">
-        <v>-85.01880580120081</v>
+        <v>-90.54024362390675</v>
       </c>
       <c r="D81">
-        <v>238.8491941987992</v>
+        <v>237.9197563760933</v>
       </c>
       <c r="E81">
-        <v>213.268</v>
+        <v>217.86</v>
       </c>
       <c r="F81">
-        <v>362.768</v>
+        <v>367.36</v>
       </c>
       <c r="G81">
         <v>38.9</v>
@@ -7929,28 +7929,28 @@
         <v>51.4</v>
       </c>
       <c r="M81">
-        <v>32.64912</v>
+        <v>33.0624</v>
       </c>
       <c r="N81">
-        <v>18.75088</v>
+        <v>18.3376</v>
       </c>
       <c r="O81">
-        <v>4.837727039999999</v>
+        <v>4.731100800000001</v>
       </c>
       <c r="P81">
-        <v>13.91315296</v>
+        <v>13.6064992</v>
       </c>
       <c r="Q81">
-        <v>64.01315296</v>
+        <v>63.7064992</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1424457887177573</v>
+        <v>0.1469492411549309</v>
       </c>
       <c r="T81">
-        <v>2.232004358377768</v>
+        <v>2.336010188335585</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.574315019822893</v>
+        <v>1.554636082075107</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08281384823098617</v>
+        <v>0.08295788083124328</v>
       </c>
       <c r="C82">
-        <v>-90.54024362390675</v>
+        <v>-96.05447601167447</v>
       </c>
       <c r="D82">
-        <v>237.9197563760933</v>
+        <v>236.9975239883256</v>
       </c>
       <c r="E82">
-        <v>217.86</v>
+        <v>222.452</v>
       </c>
       <c r="F82">
-        <v>367.36</v>
+        <v>371.952</v>
       </c>
       <c r="G82">
         <v>38.9</v>
@@ -8011,28 +8011,28 @@
         <v>51.4</v>
       </c>
       <c r="M82">
-        <v>33.0624</v>
+        <v>33.47568</v>
       </c>
       <c r="N82">
-        <v>18.3376</v>
+        <v>17.92432</v>
       </c>
       <c r="O82">
-        <v>4.731100800000001</v>
+        <v>4.62447456</v>
       </c>
       <c r="P82">
-        <v>13.6064992</v>
+        <v>13.29984544</v>
       </c>
       <c r="Q82">
-        <v>63.7064992</v>
+        <v>63.39984544000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1469492411549309</v>
+        <v>0.15192674121707</v>
       </c>
       <c r="T82">
-        <v>2.336010188335585</v>
+        <v>2.450964000394226</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.554636082075107</v>
+        <v>1.535443044024797</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08295788083124328</v>
+        <v>0.08310191343150042</v>
       </c>
       <c r="C83">
-        <v>-96.05447601167447</v>
+        <v>-101.5615864308016</v>
       </c>
       <c r="D83">
-        <v>236.9975239883256</v>
+        <v>236.0824135691985</v>
       </c>
       <c r="E83">
-        <v>222.452</v>
+        <v>227.044</v>
       </c>
       <c r="F83">
-        <v>371.952</v>
+        <v>376.544</v>
       </c>
       <c r="G83">
         <v>38.9</v>
@@ -8093,28 +8093,28 @@
         <v>51.4</v>
       </c>
       <c r="M83">
-        <v>33.47568</v>
+        <v>33.88896</v>
       </c>
       <c r="N83">
-        <v>17.92432</v>
+        <v>17.51103999999999</v>
       </c>
       <c r="O83">
-        <v>4.62447456</v>
+        <v>4.517848319999999</v>
       </c>
       <c r="P83">
-        <v>13.29984544</v>
+        <v>12.99319168</v>
       </c>
       <c r="Q83">
-        <v>63.39984544000001</v>
+        <v>63.09319168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.15192674121707</v>
+        <v>0.157457296841669</v>
       </c>
       <c r="T83">
-        <v>2.450964000394226</v>
+        <v>2.57869045823716</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.535443044024797</v>
+        <v>1.516718128853762</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08310191343150042</v>
+        <v>0.121227609973872</v>
       </c>
       <c r="C84">
-        <v>-101.5615864308016</v>
+        <v>-225.4839809885476</v>
       </c>
       <c r="D84">
-        <v>236.0824135691985</v>
+        <v>116.7520190114524</v>
       </c>
       <c r="E84">
-        <v>227.044</v>
+        <v>231.636</v>
       </c>
       <c r="F84">
-        <v>376.544</v>
+        <v>381.136</v>
       </c>
       <c r="G84">
         <v>38.9</v>
@@ -8175,45 +8175,45 @@
         <v>51.4</v>
       </c>
       <c r="M84">
-        <v>33.88896</v>
+        <v>55.95076480000001</v>
       </c>
       <c r="N84">
-        <v>17.51103999999999</v>
+        <v>-4.55076480000001</v>
       </c>
       <c r="O84">
-        <v>4.517848319999999</v>
+        <v>-1.174097318400003</v>
       </c>
       <c r="P84">
-        <v>12.99319168</v>
+        <v>-3.376667481600007</v>
       </c>
       <c r="Q84">
-        <v>63.09319168</v>
+        <v>46.72333251839999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.157457296841669</v>
+        <v>0.1662501754970538</v>
       </c>
       <c r="T84">
-        <v>2.57869045823716</v>
+        <v>2.78175924935459</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.258</v>
+        <v>0.2370155269084007</v>
       </c>
       <c r="W84">
-        <v>0.06677999999999999</v>
+        <v>0.1120061206498468</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.516718128853762</v>
+        <v>0.9186648329782972</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.121227609973872</v>
+        <v>0.122237609973872</v>
       </c>
       <c r="C85">
-        <v>-225.4839809885476</v>
+        <v>-231.6186710234907</v>
       </c>
       <c r="D85">
-        <v>116.7520190114524</v>
+        <v>115.2093289765093</v>
       </c>
       <c r="E85">
-        <v>231.636</v>
+        <v>236.228</v>
       </c>
       <c r="F85">
-        <v>381.136</v>
+        <v>385.728</v>
       </c>
       <c r="G85">
         <v>38.9</v>
@@ -8257,37 +8257,37 @@
         <v>51.4</v>
       </c>
       <c r="M85">
-        <v>55.95076480000001</v>
+        <v>56.62487040000001</v>
       </c>
       <c r="N85">
-        <v>-4.55076480000001</v>
+        <v>-5.224870400000007</v>
       </c>
       <c r="O85">
-        <v>-1.174097318400003</v>
+        <v>-1.348016563200002</v>
       </c>
       <c r="P85">
-        <v>-3.376667481600007</v>
+        <v>-3.876853836800005</v>
       </c>
       <c r="Q85">
-        <v>46.72333251839999</v>
+        <v>46.2231461632</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1662501754970538</v>
+        <v>0.1737783114656196</v>
       </c>
       <c r="T85">
-        <v>2.78175924935459</v>
+        <v>2.955619202439252</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2370155269084007</v>
+        <v>0.2341939134928245</v>
       </c>
       <c r="W85">
-        <v>0.1120061206498468</v>
+        <v>0.1124203334992534</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9186648329782972</v>
+        <v>0.9077283468714128</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.122237609973872</v>
+        <v>0.123247609973872</v>
       </c>
       <c r="C86">
-        <v>-231.6186710234907</v>
+        <v>-237.7131243891341</v>
       </c>
       <c r="D86">
-        <v>115.2093289765093</v>
+        <v>113.7068756108659</v>
       </c>
       <c r="E86">
-        <v>236.228</v>
+        <v>240.82</v>
       </c>
       <c r="F86">
-        <v>385.728</v>
+        <v>390.32</v>
       </c>
       <c r="G86">
         <v>38.9</v>
@@ -8339,37 +8339,37 @@
         <v>51.4</v>
       </c>
       <c r="M86">
-        <v>56.6248704</v>
+        <v>57.298976</v>
       </c>
       <c r="N86">
-        <v>-5.2248704</v>
+        <v>-5.898976000000005</v>
       </c>
       <c r="O86">
-        <v>-1.3480165632</v>
+        <v>-1.521935808000001</v>
       </c>
       <c r="P86">
-        <v>-3.876853836800001</v>
+        <v>-4.377040192000003</v>
       </c>
       <c r="Q86">
-        <v>46.2231461632</v>
+        <v>45.722959808</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1737783114656196</v>
+        <v>0.1823101988966609</v>
       </c>
       <c r="T86">
-        <v>2.95561920243925</v>
+        <v>3.152660482601867</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2341939134928245</v>
+        <v>0.2314386909811442</v>
       </c>
       <c r="W86">
-        <v>0.1124203334992534</v>
+        <v>0.112824800163968</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9077283468714129</v>
+        <v>0.8970491898493962</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.123247609973872</v>
+        <v>0.124257609973872</v>
       </c>
       <c r="C87">
-        <v>-237.7131243891341</v>
+        <v>-243.7688950087747</v>
       </c>
       <c r="D87">
-        <v>113.7068756108659</v>
+        <v>112.2431049912253</v>
       </c>
       <c r="E87">
-        <v>240.82</v>
+        <v>245.412</v>
       </c>
       <c r="F87">
-        <v>390.32</v>
+        <v>394.912</v>
       </c>
       <c r="G87">
         <v>38.9</v>
@@ -8421,37 +8421,37 @@
         <v>51.4</v>
       </c>
       <c r="M87">
-        <v>57.298976</v>
+        <v>57.9730816</v>
       </c>
       <c r="N87">
-        <v>-5.898976000000005</v>
+        <v>-6.573081600000002</v>
       </c>
       <c r="O87">
-        <v>-1.521935808000001</v>
+        <v>-1.6958550528</v>
       </c>
       <c r="P87">
-        <v>-4.377040192000003</v>
+        <v>-4.877226547200001</v>
       </c>
       <c r="Q87">
-        <v>45.722959808</v>
+        <v>45.2227734528</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1823101988966609</v>
+        <v>0.1920609273892795</v>
       </c>
       <c r="T87">
-        <v>3.152660482601867</v>
+        <v>3.37785051707343</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2314386909811442</v>
+        <v>0.228747543411596</v>
       </c>
       <c r="W87">
-        <v>0.112824800163968</v>
+        <v>0.1132198606271777</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8970491898493962</v>
+        <v>0.8866183853162637</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.124257609973872</v>
+        <v>0.125267609973872</v>
       </c>
       <c r="C88">
-        <v>-243.7688950087747</v>
+        <v>-249.7874578068557</v>
       </c>
       <c r="D88">
-        <v>112.2431049912253</v>
+        <v>110.8165421931443</v>
       </c>
       <c r="E88">
-        <v>245.412</v>
+        <v>250.004</v>
       </c>
       <c r="F88">
-        <v>394.912</v>
+        <v>399.504</v>
       </c>
       <c r="G88">
         <v>38.9</v>
@@ -8503,37 +8503,37 @@
         <v>51.4</v>
       </c>
       <c r="M88">
-        <v>57.9730816</v>
+        <v>58.6471872</v>
       </c>
       <c r="N88">
-        <v>-6.573081600000002</v>
+        <v>-7.247187199999999</v>
       </c>
       <c r="O88">
-        <v>-1.6958550528</v>
+        <v>-1.8697742976</v>
       </c>
       <c r="P88">
-        <v>-4.877226547200001</v>
+        <v>-5.3774129024</v>
       </c>
       <c r="Q88">
-        <v>45.2227734528</v>
+        <v>44.7225870976</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1920609273892795</v>
+        <v>0.2033117679576856</v>
       </c>
       <c r="T88">
-        <v>3.37785051707343</v>
+        <v>3.637685172232924</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.228747543411596</v>
+        <v>0.2261182613034168</v>
       </c>
       <c r="W88">
-        <v>0.1132198606271777</v>
+        <v>0.1136058392406584</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8866183853162637</v>
+        <v>0.8764273693930883</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.125267609973872</v>
+        <v>0.126277609973872</v>
       </c>
       <c r="C89">
-        <v>-249.7874578068557</v>
+        <v>-255.7702136661738</v>
       </c>
       <c r="D89">
-        <v>110.8165421931443</v>
+        <v>109.4257863338263</v>
       </c>
       <c r="E89">
-        <v>250.004</v>
+        <v>254.596</v>
       </c>
       <c r="F89">
-        <v>399.504</v>
+        <v>404.096</v>
       </c>
       <c r="G89">
         <v>38.9</v>
@@ -8585,37 +8585,37 @@
         <v>51.4</v>
       </c>
       <c r="M89">
-        <v>58.6471872</v>
+        <v>59.32129280000001</v>
       </c>
       <c r="N89">
-        <v>-7.247187199999999</v>
+        <v>-7.92129280000001</v>
       </c>
       <c r="O89">
-        <v>-1.8697742976</v>
+        <v>-2.043693542400003</v>
       </c>
       <c r="P89">
-        <v>-5.3774129024</v>
+        <v>-5.877599257600007</v>
       </c>
       <c r="Q89">
-        <v>44.7225870976</v>
+        <v>44.2224007424</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2033117679576856</v>
+        <v>0.2164377486208261</v>
       </c>
       <c r="T89">
-        <v>3.637685172232924</v>
+        <v>3.940825603252335</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2261182613034168</v>
+        <v>0.223548735606787</v>
       </c>
       <c r="W89">
-        <v>0.1136058392406584</v>
+        <v>0.1139830456129237</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8764273693930883</v>
+        <v>0.8664679674681667</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.126277609973872</v>
+        <v>0.127287609973872</v>
       </c>
       <c r="C90">
-        <v>-255.7702136661738</v>
+        <v>-261.7184940164331</v>
       </c>
       <c r="D90">
-        <v>109.4257863338263</v>
+        <v>108.0695059835669</v>
       </c>
       <c r="E90">
-        <v>254.596</v>
+        <v>259.188</v>
       </c>
       <c r="F90">
-        <v>404.096</v>
+        <v>408.688</v>
       </c>
       <c r="G90">
         <v>38.9</v>
@@ -8667,37 +8667,37 @@
         <v>51.4</v>
       </c>
       <c r="M90">
-        <v>59.32129280000001</v>
+        <v>59.99539840000001</v>
       </c>
       <c r="N90">
-        <v>-7.92129280000001</v>
+        <v>-8.595398400000008</v>
       </c>
       <c r="O90">
-        <v>-2.043693542400003</v>
+        <v>-2.217612787200002</v>
       </c>
       <c r="P90">
-        <v>-5.877599257600007</v>
+        <v>-6.377785612800006</v>
       </c>
       <c r="Q90">
-        <v>44.2224007424</v>
+        <v>43.7222143872</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2164377486208261</v>
+        <v>0.2319502712227194</v>
       </c>
       <c r="T90">
-        <v>3.940825603252335</v>
+        <v>4.299082476275275</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.223548735606787</v>
+        <v>0.2210369520606434</v>
       </c>
       <c r="W90">
-        <v>0.1139830456129237</v>
+        <v>0.1143517754374976</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8664679674681667</v>
+        <v>0.856732372328075</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.127287609973872</v>
+        <v>0.128297609973872</v>
       </c>
       <c r="C91">
-        <v>-261.7184940164331</v>
+        <v>-267.6335650857401</v>
       </c>
       <c r="D91">
-        <v>108.0695059835669</v>
+        <v>106.7464349142599</v>
       </c>
       <c r="E91">
-        <v>259.188</v>
+        <v>263.78</v>
       </c>
       <c r="F91">
-        <v>408.688</v>
+        <v>413.28</v>
       </c>
       <c r="G91">
         <v>38.9</v>
@@ -8749,37 +8749,37 @@
         <v>51.4</v>
       </c>
       <c r="M91">
-        <v>59.99539840000001</v>
+        <v>60.669504</v>
       </c>
       <c r="N91">
-        <v>-8.595398400000008</v>
+        <v>-9.269504000000005</v>
       </c>
       <c r="O91">
-        <v>-2.217612787200002</v>
+        <v>-2.391532032000002</v>
       </c>
       <c r="P91">
-        <v>-6.377785612800006</v>
+        <v>-6.877971968000003</v>
       </c>
       <c r="Q91">
-        <v>43.7222143872</v>
+        <v>43.222028032</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2319502712227194</v>
+        <v>0.2505652983449914</v>
       </c>
       <c r="T91">
-        <v>4.299082476275275</v>
+        <v>4.728990723902802</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2210369520606434</v>
+        <v>0.2185809859266362</v>
       </c>
       <c r="W91">
-        <v>0.1143517754374976</v>
+        <v>0.1147123112659698</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.856732372328075</v>
+        <v>0.8472131237466519</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.128297609973872</v>
+        <v>0.129307609973872</v>
       </c>
       <c r="C92">
-        <v>-267.6335650857401</v>
+        <v>-273.5166318435738</v>
       </c>
       <c r="D92">
-        <v>106.7464349142599</v>
+        <v>105.4553681564262</v>
       </c>
       <c r="E92">
-        <v>263.78</v>
+        <v>268.372</v>
       </c>
       <c r="F92">
-        <v>413.28</v>
+        <v>417.872</v>
       </c>
       <c r="G92">
         <v>38.9</v>
@@ -8831,37 +8831,37 @@
         <v>51.4</v>
       </c>
       <c r="M92">
-        <v>60.669504</v>
+        <v>61.34360960000001</v>
       </c>
       <c r="N92">
-        <v>-9.269504000000005</v>
+        <v>-9.943609600000009</v>
       </c>
       <c r="O92">
-        <v>-2.391532032000002</v>
+        <v>-2.565451276800002</v>
       </c>
       <c r="P92">
-        <v>-6.877971968000003</v>
+        <v>-7.378158323200006</v>
       </c>
       <c r="Q92">
-        <v>43.222028032</v>
+        <v>42.7218416768</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2505652983449914</v>
+        <v>0.2733169981611015</v>
       </c>
       <c r="T92">
-        <v>4.728990723902802</v>
+        <v>5.25443413766978</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2185809859266362</v>
+        <v>0.2161789970702996</v>
       </c>
       <c r="W92">
-        <v>0.1147123112659698</v>
+        <v>0.11506492323008</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8472131237466519</v>
+        <v>0.8379030894197657</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.129307609973872</v>
+        <v>0.130317609973872</v>
       </c>
       <c r="C93">
-        <v>-273.5166318435738</v>
+        <v>-279.3688416610416</v>
       </c>
       <c r="D93">
-        <v>105.4553681564262</v>
+        <v>104.1951583389584</v>
       </c>
       <c r="E93">
-        <v>268.372</v>
+        <v>272.964</v>
       </c>
       <c r="F93">
-        <v>417.872</v>
+        <v>422.464</v>
       </c>
       <c r="G93">
         <v>38.9</v>
@@ -8913,37 +8913,37 @@
         <v>51.4</v>
       </c>
       <c r="M93">
-        <v>61.34360960000001</v>
+        <v>62.0177152</v>
       </c>
       <c r="N93">
-        <v>-9.943609600000009</v>
+        <v>-10.61771520000001</v>
       </c>
       <c r="O93">
-        <v>-2.565451276800002</v>
+        <v>-2.739370521600001</v>
       </c>
       <c r="P93">
-        <v>-7.378158323200006</v>
+        <v>-7.878344678400005</v>
       </c>
       <c r="Q93">
-        <v>42.7218416768</v>
+        <v>42.2216553216</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2733169981611015</v>
+        <v>0.3017566229312393</v>
       </c>
       <c r="T93">
-        <v>5.25443413766978</v>
+        <v>5.911238404878505</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2161789970702996</v>
+        <v>0.2138292253630137</v>
       </c>
       <c r="W93">
-        <v>0.11506492323008</v>
+        <v>0.1154098697167096</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8379030894197657</v>
+        <v>0.8287954471434639</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.130317609973872</v>
+        <v>0.131327609973872</v>
       </c>
       <c r="C94">
-        <v>-279.3688416610416</v>
+        <v>-285.1912877117906</v>
       </c>
       <c r="D94">
-        <v>104.1951583389584</v>
+        <v>102.9647122882094</v>
       </c>
       <c r="E94">
-        <v>272.964</v>
+        <v>277.556</v>
       </c>
       <c r="F94">
-        <v>422.464</v>
+        <v>427.056</v>
       </c>
       <c r="G94">
         <v>38.9</v>
@@ -8995,37 +8995,37 @@
         <v>51.4</v>
       </c>
       <c r="M94">
-        <v>62.0177152</v>
+        <v>62.69182080000001</v>
       </c>
       <c r="N94">
-        <v>-10.61771520000001</v>
+        <v>-11.29182080000001</v>
       </c>
       <c r="O94">
-        <v>-2.739370521600001</v>
+        <v>-2.913289766400003</v>
       </c>
       <c r="P94">
-        <v>-7.878344678400005</v>
+        <v>-8.378531033600009</v>
       </c>
       <c r="Q94">
-        <v>42.2216553216</v>
+        <v>41.7214689664</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3017566229312393</v>
+        <v>0.3383218547785593</v>
       </c>
       <c r="T94">
-        <v>5.911238404878505</v>
+        <v>6.755701034146863</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2138292253630137</v>
+        <v>0.2115299863806157</v>
       </c>
       <c r="W94">
-        <v>0.1154098697167096</v>
+        <v>0.1157473979993256</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8287954471434639</v>
+        <v>0.8198836681419212</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.131327609973872</v>
+        <v>0.132337609973872</v>
       </c>
       <c r="C95">
-        <v>-285.1912877117906</v>
+        <v>-290.9850121347611</v>
       </c>
       <c r="D95">
-        <v>102.9647122882094</v>
+        <v>101.762987865239</v>
       </c>
       <c r="E95">
-        <v>277.556</v>
+        <v>282.148</v>
       </c>
       <c r="F95">
-        <v>427.056</v>
+        <v>431.648</v>
       </c>
       <c r="G95">
         <v>38.9</v>
@@ -9077,37 +9077,37 @@
         <v>51.4</v>
       </c>
       <c r="M95">
-        <v>62.69182080000001</v>
+        <v>63.36592640000001</v>
       </c>
       <c r="N95">
-        <v>-11.29182080000001</v>
+        <v>-11.96592640000001</v>
       </c>
       <c r="O95">
-        <v>-2.913289766400003</v>
+        <v>-3.087209011200002</v>
       </c>
       <c r="P95">
-        <v>-8.378531033600009</v>
+        <v>-8.878717388800005</v>
       </c>
       <c r="Q95">
-        <v>41.7214689664</v>
+        <v>41.2212826112</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3383218547785593</v>
+        <v>0.3870754972416525</v>
       </c>
       <c r="T95">
-        <v>6.755701034146863</v>
+        <v>7.881651206504676</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2115299863806157</v>
+        <v>0.2092796673765666</v>
       </c>
       <c r="W95">
-        <v>0.1157473979993256</v>
+        <v>0.11607774482912</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8198836681419212</v>
+        <v>0.8111615014595603</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.132337609973872</v>
+        <v>0.133347609973872</v>
       </c>
       <c r="C96">
-        <v>-290.9850121347611</v>
+        <v>-296.7510089780166</v>
       </c>
       <c r="D96">
-        <v>101.762987865239</v>
+        <v>100.5889910219835</v>
       </c>
       <c r="E96">
-        <v>282.148</v>
+        <v>286.74</v>
       </c>
       <c r="F96">
-        <v>431.648</v>
+        <v>436.24</v>
       </c>
       <c r="G96">
         <v>38.9</v>
@@ -9159,37 +9159,37 @@
         <v>51.4</v>
       </c>
       <c r="M96">
-        <v>63.36592640000001</v>
+        <v>64.04003200000001</v>
       </c>
       <c r="N96">
-        <v>-11.96592640000001</v>
+        <v>-12.64003200000001</v>
       </c>
       <c r="O96">
-        <v>-3.087209011200002</v>
+        <v>-3.261128256000003</v>
       </c>
       <c r="P96">
-        <v>-8.878717388800005</v>
+        <v>-9.378903744000009</v>
       </c>
       <c r="Q96">
-        <v>41.2212826112</v>
+        <v>40.721096256</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3870754972416525</v>
+        <v>0.4553305966899833</v>
       </c>
       <c r="T96">
-        <v>7.881651206504676</v>
+        <v>9.457981447805617</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2092796673765666</v>
+        <v>0.2070767235094448</v>
       </c>
       <c r="W96">
-        <v>0.11607774482912</v>
+        <v>0.1164011369888135</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8111615014595603</v>
+        <v>0.8026229593389334</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.133347609973872</v>
+        <v>0.1875461874654034</v>
       </c>
       <c r="C97">
-        <v>-296.7510089780166</v>
+        <v>-339.8045741332033</v>
       </c>
       <c r="D97">
-        <v>100.5889910219835</v>
+        <v>62.12742586679668</v>
       </c>
       <c r="E97">
-        <v>286.74</v>
+        <v>291.3320000000001</v>
       </c>
       <c r="F97">
-        <v>436.24</v>
+        <v>440.8320000000001</v>
       </c>
       <c r="G97">
         <v>38.9</v>
@@ -9241,45 +9241,45 @@
         <v>51.4</v>
       </c>
       <c r="M97">
-        <v>64.04003200000001</v>
+        <v>88.51906560000002</v>
       </c>
       <c r="N97">
-        <v>-12.64003200000001</v>
+        <v>-37.11906560000002</v>
       </c>
       <c r="O97">
-        <v>-3.261128256000003</v>
+        <v>-9.576718924800005</v>
       </c>
       <c r="P97">
-        <v>-9.378903744000009</v>
+        <v>-27.54234667520002</v>
       </c>
       <c r="Q97">
-        <v>40.721096256</v>
+        <v>22.55765332479999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4553305966899833</v>
+        <v>0.5914276831507653</v>
       </c>
       <c r="T97">
-        <v>9.457981447805617</v>
+        <v>12.60110122750035</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.2070767235094448</v>
+        <v>0.1498117937657037</v>
       </c>
       <c r="W97">
-        <v>0.1164011369888135</v>
+        <v>0.1707177918118467</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8026229593389334</v>
+        <v>0.5806658673089291</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1875461874654034</v>
+        <v>0.1890961874654034</v>
       </c>
       <c r="C98">
-        <v>-339.8045741332032</v>
+        <v>-345.0685913850006</v>
       </c>
       <c r="D98">
-        <v>62.12742586679673</v>
+        <v>61.45540861499939</v>
       </c>
       <c r="E98">
-        <v>291.332</v>
+        <v>295.924</v>
       </c>
       <c r="F98">
-        <v>440.832</v>
+        <v>445.424</v>
       </c>
       <c r="G98">
         <v>38.9</v>
@@ -9323,37 +9323,37 @@
         <v>51.4</v>
       </c>
       <c r="M98">
-        <v>88.5190656</v>
+        <v>89.44113919999999</v>
       </c>
       <c r="N98">
-        <v>-37.11906560000001</v>
+        <v>-38.0411392</v>
       </c>
       <c r="O98">
-        <v>-9.576718924800002</v>
+        <v>-9.814613913599999</v>
       </c>
       <c r="P98">
-        <v>-27.5423466752</v>
+        <v>-28.2265252864</v>
       </c>
       <c r="Q98">
-        <v>22.5576533248</v>
+        <v>21.8734747136</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5914276831507638</v>
+        <v>0.7733035775343516</v>
       </c>
       <c r="T98">
-        <v>12.60110122750032</v>
+        <v>16.80146830333376</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1498117937657037</v>
+        <v>0.1482673422835831</v>
       </c>
       <c r="W98">
-        <v>0.1707177918118467</v>
+        <v>0.1710279176694565</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5806658673089291</v>
+        <v>0.574679621254198</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1890961874654034</v>
+        <v>0.1906461874654034</v>
       </c>
       <c r="C99">
-        <v>-345.0685913850006</v>
+        <v>-350.318226114779</v>
       </c>
       <c r="D99">
-        <v>61.45540861499939</v>
+        <v>60.79777388522095</v>
       </c>
       <c r="E99">
-        <v>295.924</v>
+        <v>300.516</v>
       </c>
       <c r="F99">
-        <v>445.424</v>
+        <v>450.016</v>
       </c>
       <c r="G99">
         <v>38.9</v>
@@ -9405,37 +9405,37 @@
         <v>51.4</v>
       </c>
       <c r="M99">
-        <v>89.44113919999999</v>
+        <v>90.3632128</v>
       </c>
       <c r="N99">
-        <v>-38.0411392</v>
+        <v>-38.9632128</v>
       </c>
       <c r="O99">
-        <v>-9.814613913599999</v>
+        <v>-10.0525089024</v>
       </c>
       <c r="P99">
-        <v>-28.2265252864</v>
+        <v>-28.9107038976</v>
       </c>
       <c r="Q99">
-        <v>21.8734747136</v>
+        <v>21.1892961024</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7733035775343516</v>
+        <v>1.137055366301528</v>
       </c>
       <c r="T99">
-        <v>16.80146830333376</v>
+        <v>25.20220245500063</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1482673422835831</v>
+        <v>0.1467544102194649</v>
       </c>
       <c r="W99">
-        <v>0.1710279176694565</v>
+        <v>0.1713317144279315</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.574679621254198</v>
+        <v>0.568815543486298</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1906461874654034</v>
+        <v>0.1921961874654034</v>
       </c>
       <c r="C100">
-        <v>-350.318226114779</v>
+        <v>-355.5539351563439</v>
       </c>
       <c r="D100">
-        <v>60.79777388522095</v>
+        <v>60.15406484365613</v>
       </c>
       <c r="E100">
-        <v>300.516</v>
+        <v>305.108</v>
       </c>
       <c r="F100">
-        <v>450.016</v>
+        <v>454.608</v>
       </c>
       <c r="G100">
         <v>38.9</v>
@@ -9487,37 +9487,37 @@
         <v>51.4</v>
       </c>
       <c r="M100">
-        <v>90.3632128</v>
+        <v>91.2852864</v>
       </c>
       <c r="N100">
-        <v>-38.9632128</v>
+        <v>-39.88528640000001</v>
       </c>
       <c r="O100">
-        <v>-10.0525089024</v>
+        <v>-10.2904038912</v>
       </c>
       <c r="P100">
-        <v>-28.9107038976</v>
+        <v>-29.5948825088</v>
       </c>
       <c r="Q100">
-        <v>21.1892961024</v>
+        <v>20.5051174912</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.137055366301528</v>
+        <v>2.228310732603055</v>
       </c>
       <c r="T100">
-        <v>25.20220245500063</v>
+        <v>50.40440491000128</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1467544102194649</v>
+        <v>0.1452720424394703</v>
       </c>
       <c r="W100">
-        <v>0.1713317144279315</v>
+        <v>0.1716293738781544</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.568815543486298</v>
+        <v>0.5630699319359314</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1921961874654034</v>
-      </c>
-      <c r="C101">
-        <v>-355.5539351563439</v>
-      </c>
-      <c r="D101">
-        <v>60.15406484365613</v>
-      </c>
-      <c r="E101">
-        <v>305.108</v>
-      </c>
-      <c r="F101">
-        <v>454.608</v>
-      </c>
-      <c r="G101">
-        <v>38.9</v>
-      </c>
-      <c r="H101">
-        <v>309.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>101.5</v>
-      </c>
-      <c r="K101">
-        <v>50.1</v>
-      </c>
-      <c r="L101">
-        <v>51.4</v>
-      </c>
-      <c r="M101">
-        <v>91.2852864</v>
-      </c>
-      <c r="N101">
-        <v>-39.88528640000001</v>
-      </c>
-      <c r="O101">
-        <v>-10.2904038912</v>
-      </c>
-      <c r="P101">
-        <v>-29.5948825088</v>
-      </c>
-      <c r="Q101">
-        <v>20.5051174912</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.228310732603055</v>
-      </c>
-      <c r="T101">
-        <v>50.40440491000128</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1452720424394703</v>
-      </c>
-      <c r="W101">
-        <v>0.1716293738781544</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5630699319359314</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
